--- a/UNION_PANEL.xlsx
+++ b/UNION_PANEL.xlsx
@@ -519,27 +519,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
+          <t>Sustainable Agriculture</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,19 +547,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>169512</v>
+        <v>14910.1</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>169512</v>
+        <v>14910.1</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -580,22 +588,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -608,27 +616,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>103391.9</v>
+        <v>22632</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>103391.9</v>
+        <v>22632</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -649,27 +649,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Climate Emergency Response</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -692,12 +692,12 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>93847.39999999999</v>
+        <v>10497.6</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>93847.39999999999</v>
+        <v>10497.6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -718,22 +718,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Environmental Quality in Cities and the Countryside</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>78582.2</v>
+        <v>30.8</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>78582.2</v>
+        <v>30.8</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -856,13 +856,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -872,7 +876,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -882,12 +886,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Demographic Shifts</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -895,12 +899,12 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>886652.4</v>
+        <v>135.5</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>886652.4</v>
+        <v>135.5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -921,18 +925,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Planning and Budgeting for Sustainable Development</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -952,7 +960,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Pandemics; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -960,12 +968,12 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>68424.8</v>
+        <v>136</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>68424.8</v>
+        <v>136</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -986,18 +994,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1017,7 +1029,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1025,12 +1037,12 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>51241.7</v>
+        <v>286.4</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>51241.7</v>
+        <v>286.4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1051,27 +1063,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1079,19 +1091,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
+        </is>
+      </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>27428.4</v>
+        <v>213.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>27428.4</v>
+        <v>213.3</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1112,22 +1132,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1140,19 +1160,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+        </is>
+      </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>22632</v>
+        <v>399.2</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>22632</v>
+        <v>399.2</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1173,22 +1201,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
+          <t>Nuclear Policy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1216,12 +1244,12 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>15913.4</v>
+        <v>467.3</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>15913.4</v>
+        <v>467.3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1242,18 +1270,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Better Cities</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Brazilian Space Programme</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Urban Development</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1268,25 +1300,25 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>16875</v>
+        <v>150.7</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>16875</v>
+        <v>150.7</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1307,28 +1339,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>National Defense</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1338,7 +1374,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Shifts in Globalisation</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1346,12 +1382,12 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>13846.4</v>
+        <v>6183</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>13846.4</v>
+        <v>6183</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1372,27 +1408,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1407,7 +1443,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1415,12 +1451,12 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>13474.9</v>
+        <v>78582.2</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>13474.9</v>
+        <v>78582.2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1441,27 +1477,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1471,12 +1507,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1484,12 +1520,12 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>13130.8</v>
+        <v>259.5</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>13130.8</v>
+        <v>259.5</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1510,22 +1546,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1538,27 +1574,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>12297.7</v>
+        <v>6546.1</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>12297.7</v>
+        <v>6546.1</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1579,12 +1607,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1594,12 +1622,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1614,7 +1642,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1622,12 +1650,12 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>8397</v>
+        <v>3396.6</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>8397</v>
+        <v>3396.6</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1648,18 +1676,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Decent Housing</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1679,20 +1711,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>6472.2</v>
+        <v>12297.7</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>6472.2</v>
+        <v>12297.7</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1713,23 +1745,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Basic Sanitation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2322</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1737,19 +1773,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>6801</v>
+        <v>2895.5</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>6801</v>
+        <v>2895.5</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1770,27 +1814,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>Tourism, This Is the Destination</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1798,27 +1842,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>6183</v>
+        <v>2557.2</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>6183</v>
+        <v>2557.2</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1839,22 +1875,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1869,12 +1905,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1882,12 +1918,12 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>4810.6</v>
+        <v>1870.2</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>4810.6</v>
+        <v>1870.2</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1908,18 +1944,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1934,12 +1974,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1947,12 +1987,12 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>4085.3</v>
+        <v>1870.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>4085.3</v>
+        <v>1870.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1973,22 +2013,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2008,7 +2048,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2016,12 +2056,12 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>4015.2</v>
+        <v>139.8</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>4015.2</v>
+        <v>139.8</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2042,27 +2082,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2072,12 +2112,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2085,12 +2125,12 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>3396.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>3396.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2111,27 +2151,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2139,19 +2179,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>2584.2</v>
+        <v>557.9</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>2584.2</v>
+        <v>557.9</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2172,17 +2220,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2200,19 +2248,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>2557.2</v>
+        <v>8397</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>2557.2</v>
+        <v>8397</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2233,27 +2289,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2261,19 +2317,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>6546.1</v>
+        <v>13130.8</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>6546.1</v>
+        <v>13130.8</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2294,23 +2358,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Road Safety</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3108</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2333,12 +2401,12 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>2102.4</v>
+        <v>328.8</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>2102.4</v>
+        <v>328.8</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2359,18 +2427,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Sustainable Popular and Solidarity Economy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2386,16 +2458,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>2026.6</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>2026.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2416,22 +2486,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Public and Government Communication</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2444,19 +2514,25 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>2000</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2477,22 +2553,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2507,12 +2583,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2520,12 +2596,12 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>1870.2</v>
+        <v>163.9</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1870.2</v>
+        <v>163.9</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2546,22 +2622,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2581,7 +2657,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2589,12 +2665,12 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>1870.2</v>
+        <v>135.2</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1870.2</v>
+        <v>135.2</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2615,23 +2691,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>5113</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2646,7 +2726,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
+          <t>Demographic Shifts; Technological Change</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2654,12 +2734,12 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>1125</v>
+        <v>14463.9</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1125</v>
+        <v>14463.9</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2680,23 +2760,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2711,12 +2795,12 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>1104.2</v>
+        <v>27428.4</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1104.2</v>
+        <v>27428.4</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2737,23 +2821,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Specialized Health Care</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>5118</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2761,19 +2849,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Pandemics</t>
+        </is>
+      </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>1054.1</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1054.1</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2794,18 +2890,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>5120</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2825,20 +2925,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>23058</v>
+        <v>4015.2</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>23058</v>
+        <v>4015.2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2859,22 +2959,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2894,7 +2994,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2902,12 +3002,12 @@
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>150.7</v>
+        <v>15913.4</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>150.7</v>
+        <v>15913.4</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2928,18 +3028,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Indigenous Health</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2952,27 +3056,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>7781</v>
+        <v>2584.2</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>7781</v>
+        <v>2584.2</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2993,27 +3089,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3021,19 +3117,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
+        </is>
+      </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>592.4</v>
+        <v>13474.9</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>592.4</v>
+        <v>13474.9</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3054,22 +3158,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3082,27 +3186,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>557.9</v>
+        <v>2000</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>557.9</v>
+        <v>2000</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3123,23 +3219,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3147,27 +3247,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>478</v>
+        <v>169512</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>478</v>
+        <v>169512</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3188,22 +3280,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3218,12 +3310,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3231,12 +3323,12 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>399.2</v>
+        <v>103391.9</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>399.2</v>
+        <v>103391.9</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3257,27 +3349,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3287,12 +3379,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3300,12 +3392,12 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>328.8</v>
+        <v>4810.6</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>328.8</v>
+        <v>4810.6</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3326,23 +3418,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3350,27 +3446,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>286.4</v>
+        <v>223.3</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>286.4</v>
+        <v>223.3</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3391,27 +3479,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>Youth: Rights, Participation and Good Living</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3419,27 +3507,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>286.4</v>
+        <v>48.8</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>286.4</v>
+        <v>48.8</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3460,13 +3540,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3487,16 +3571,16 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>264.7</v>
+        <v>592.4</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>264.7</v>
+        <v>592.4</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3517,22 +3601,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Structuring the National Care Policy</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3545,27 +3629,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>259.5</v>
+        <v>14.9</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>259.5</v>
+        <v>14.9</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3586,18 +3662,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Living Periphery</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Urban Development</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3610,27 +3690,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>337.8</v>
+        <v>631.2</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>337.8</v>
+        <v>631.2</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3651,13 +3723,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Equality in Decision-Making and Power for Women</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3682,7 +3758,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3690,12 +3766,12 @@
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>230.2</v>
+        <v>18</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>230.2</v>
+        <v>18</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3716,27 +3792,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+          <t>Black Youth Alive</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3744,19 +3820,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>223.3</v>
+        <v>12.4</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>223.3</v>
+        <v>12.4</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3777,13 +3861,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>5804</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3801,19 +3889,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>222.5</v>
+        <v>76</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>222.5</v>
+        <v>76</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3834,23 +3930,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>5812</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3858,27 +3958,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>215.9</v>
+        <v>27.2</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>215.9</v>
+        <v>27.2</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3899,23 +3991,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3923,27 +4019,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Climate Change</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>1905.3</v>
+        <v>18.1</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>1905.3</v>
+        <v>18.1</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3964,22 +4052,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>5815</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3999,7 +4087,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Demographic Shifts</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -4007,12 +4095,12 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>213.3</v>
+        <v>20.1</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>213.3</v>
+        <v>20.1</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4033,22 +4121,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4058,17 +4146,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4076,12 +4164,12 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>163.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>163.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4102,23 +4190,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>5838</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4126,27 +4218,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Climate Change; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4167,22 +4251,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4197,12 +4281,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4210,12 +4294,12 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>139.8</v>
+        <v>800.8</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>139.8</v>
+        <v>800.8</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4236,22 +4320,18 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2224</t>
-        </is>
-      </c>
+          <t>Basic Education Democratic, with Quality and Equity</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4271,7 +4351,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Demographic Shifts; Pandemics; Technological Change</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -4279,12 +4359,12 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>136</v>
+        <v>68424.8</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>136</v>
+        <v>68424.8</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4305,22 +4385,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
+          <t>Better Cities</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Urban Development</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4340,20 +4416,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>135.5</v>
+        <v>16875</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>135.5</v>
+        <v>16875</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4374,22 +4450,18 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
+          <t>Communications for Inclusion and Transformation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4409,7 +4481,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4417,12 +4489,12 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>135.2</v>
+        <v>2102.4</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>135.2</v>
+        <v>2102.4</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4443,23 +4515,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
+          <t>Cooperation of Defence for National Development</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4467,27 +4539,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>122.3</v>
+        <v>1054.1</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>122.3</v>
+        <v>1054.1</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4508,23 +4572,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4532,19 +4596,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding; Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>108.1</v>
+        <v>478</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>108.1</v>
+        <v>478</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4565,14 +4637,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
+          <t>Economic Autonomy of Women</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -4590,7 +4658,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4600,7 +4668,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4608,12 +4676,12 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>90.40000000000001</v>
+        <v>122.3</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>90.40000000000001</v>
+        <v>122.3</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4634,27 +4702,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
+          <t>Electric Energy</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4662,19 +4726,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Climate Change; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4695,22 +4767,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
+          <t>Family Farming and Agroecology</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4725,12 +4793,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4738,12 +4806,12 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>76</v>
+        <v>7781</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>76</v>
+        <v>7781</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4764,22 +4832,18 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4792,27 +4856,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>66.90000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>66.90000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4833,27 +4889,23 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2306</t>
-        </is>
-      </c>
+          <t>Institutional Security</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4868,7 +4920,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Technological Change</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4876,12 +4928,12 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>467.3</v>
+        <v>45</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>467.3</v>
+        <v>45</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4902,7 +4954,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -4913,12 +4965,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,12 +4980,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
+          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4941,12 +4993,12 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>74.3</v>
+        <v>1125</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>74.3</v>
+        <v>1125</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4967,47 +5019,51 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>5135</t>
-        </is>
-      </c>
+          <t>National Defense</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding; Shifts in Globalisation</t>
+        </is>
+      </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>48.8</v>
+        <v>13846.4</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>48.8</v>
+        <v>13846.4</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5028,23 +5084,23 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
+          <t>Ocean, Coastal Zone and Antarctica</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5054,12 +5110,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5067,12 +5123,12 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>45</v>
+        <v>50.4</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5093,13 +5149,13 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5117,27 +5173,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>42.1</v>
+        <v>264.7</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>42.1</v>
+        <v>264.7</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5158,18 +5206,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ocean, Coastal Zone and Antarctica</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5189,7 +5237,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5197,12 +5245,12 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>50.4</v>
+        <v>42.1</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>50.4</v>
+        <v>42.1</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5223,27 +5271,23 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
+          <t>Primary Health Care</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,12 +5297,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5266,12 +5310,12 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>30.8</v>
+        <v>51241.7</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>30.8</v>
+        <v>51241.7</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5292,23 +5336,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
+          <t>Professional and Technological Education that Transforms</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5316,19 +5360,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Increased Polarisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>28</v>
+        <v>4085.3</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>28</v>
+        <v>4085.3</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5349,22 +5401,18 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5377,19 +5425,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>27.2</v>
+        <v>337.8</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>27.2</v>
+        <v>337.8</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5410,18 +5466,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
+          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5441,7 +5497,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -5449,12 +5505,12 @@
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>34.8</v>
+        <v>158.2</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>34.8</v>
+        <v>158.2</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5475,14 +5531,10 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>5815</t>
-        </is>
-      </c>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -5490,12 +5542,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5510,7 +5562,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Demographic Shifts</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -5518,12 +5570,12 @@
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>20.1</v>
+        <v>34.8</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>20.1</v>
+        <v>34.8</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -5544,22 +5596,18 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5572,19 +5620,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>18.1</v>
+        <v>800.8</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>18.1</v>
+        <v>800.8</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5605,14 +5661,10 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Equality in Decision-Making and Power for Women</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>5661</t>
-        </is>
-      </c>
+          <t>Public Security with Citizenship</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -5620,12 +5672,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5635,12 +5687,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Biodiversity Loss; Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -5648,12 +5700,12 @@
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>18</v>
+        <v>5354.6</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>18</v>
+        <v>5354.6</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5674,22 +5726,18 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Climate Emergency Response</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
+          <t>Rail Transport</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5702,27 +5750,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Climate Change</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>10497.6</v>
+        <v>1104.2</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>10497.6</v>
+        <v>1104.2</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5743,22 +5783,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Structuring the National Care Policy</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>5501</t>
-        </is>
-      </c>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5771,19 +5807,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>14.9</v>
+        <v>74.3</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>14.9</v>
+        <v>74.3</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -5804,22 +5848,18 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Black Youth Alive</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>5803</t>
-        </is>
-      </c>
+          <t>Right to Culture</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5832,27 +5872,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>12.4</v>
+        <v>2026.6</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>12.4</v>
+        <v>2026.6</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5873,23 +5905,23 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Water Resources: Water in Quantity and Quality Forever</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5897,27 +5929,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>2176.2</v>
+        <v>222.5</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>2176.2</v>
+        <v>222.5</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -5938,27 +5962,23 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Basic Sanitation</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
+          <t>Risk and Disaster Management</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5973,7 +5993,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5981,12 +6001,12 @@
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>2895.5</v>
+        <v>1905.3</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>2895.5</v>
+        <v>1905.3</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6007,27 +6027,23 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>6114</t>
-        </is>
-      </c>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6035,27 +6051,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>800.8</v>
+        <v>6801</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>800.8</v>
+        <v>6801</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6076,18 +6084,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6102,25 +6110,25 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>800.8</v>
+        <v>6472.2</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>800.8</v>
+        <v>6472.2</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6141,18 +6149,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Public Security with Citizenship</t>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6167,12 +6175,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Technological Change</t>
+          <t>Demographic Shifts</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -6180,12 +6188,12 @@
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>5354.6</v>
+        <v>886652.4</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>5354.6</v>
+        <v>886652.4</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6206,27 +6214,23 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6234,27 +6238,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Demographic Shifts; Technological Change</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>14463.9</v>
+        <v>28</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>14463.9</v>
+        <v>28</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6275,22 +6271,18 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Living Periphery</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
+          <t>State Transformation for Citizenship and Development</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Urban Development</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6303,19 +6295,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
-        <v>631.2</v>
+        <v>286.4</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
-        <v>631.2</v>
+        <v>286.4</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6336,18 +6336,18 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
+          <t>Supply and Food Sovereignty</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6367,20 +6367,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>158.2</v>
+        <v>23058</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
-        <v>158.2</v>
+        <v>23058</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6401,14 +6401,10 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sustainable Agriculture</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
+          <t>Sustainable Fisheries and Aquaculture</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Agriculture</t>
@@ -6431,12 +6427,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6444,12 +6440,12 @@
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>14910.1</v>
+        <v>215.9</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
-        <v>14910.1</v>
+        <v>215.9</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -6470,22 +6466,18 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Public and Government Communication</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
+          <t>Water Resources: Water in Quantity and Quality Forever</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6500,23 +6492,25 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>2176.2</v>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2176.2</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6537,22 +6531,18 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sustainable Popular and Solidarity Economy</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>4006</t>
-        </is>
-      </c>
+          <t>Women Living Free from Violence</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6565,17 +6555,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="M94" t="n">
+        <v>230.2</v>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>230.2</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
+          <t>Sustainable Agriculture</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>169512</v>
+        <v>14910.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13058,12 +13058,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>103391.9</v>
+        <v>22632</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Climate Emergency Response</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>93847.39999999999</v>
+        <v>10497.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Environmental Quality in Cities and the Countryside</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78582.2</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>886652.4</v>
+        <v>135.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
+          <t>Planning and Budgeting for Sustainable Development</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68424.8</v>
+        <v>136</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>51241.7</v>
+        <v>286.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>27428.4</v>
+        <v>213.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -13338,12 +13338,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22632</v>
+        <v>399.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
+          <t>Nuclear Policy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15913.4</v>
+        <v>467.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Better Cities</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16875</v>
+        <v>150.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>National Defense</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13846.4</v>
+        <v>6183</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -13478,12 +13478,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13474.9</v>
+        <v>78582.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13130.8</v>
+        <v>259.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12297.7</v>
+        <v>6546.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>8397</v>
+        <v>3396.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13644,7 +13644,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6472.2</v>
+        <v>12297.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+          <t>Basic Sanitation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6801</v>
+        <v>2895.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -13688,12 +13688,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>Tourism, This Is the Destination</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6183</v>
+        <v>2557.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4810.6</v>
+        <v>1870.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4085.3</v>
+        <v>1870.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4015.2</v>
+        <v>139.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3396.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2584.2</v>
+        <v>557.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2557.2</v>
+        <v>8397</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13959,7 +13959,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6546.1</v>
+        <v>13130.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -13968,12 +13968,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
+          <t>Road Safety</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13994,7 +13994,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2102.4</v>
+        <v>328.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -14003,12 +14003,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14029,7 +14029,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2026.6</v>
+        <v>163.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2000</v>
+        <v>135.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -14073,12 +14073,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1870.2</v>
+        <v>14463.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1870.2</v>
+        <v>27428.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14169,7 +14169,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1125</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1104.2</v>
+        <v>4015.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -14213,12 +14213,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1054.1</v>
+        <v>15913.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14265,7 +14265,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
+          <t>Indigenous Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>23058</v>
+        <v>2584.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>150.7</v>
+        <v>13474.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7781</v>
+        <v>2000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14379,7 +14379,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>592.4</v>
+        <v>169512</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>557.9</v>
+        <v>103391.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -14423,12 +14423,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14449,7 +14449,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>478</v>
+        <v>4810.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>399.2</v>
+        <v>223.3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -14493,12 +14493,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>Youth: Rights, Participation and Good Living</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>328.8</v>
+        <v>48.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>286.4</v>
+        <v>592.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>Structuring the National Care Policy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>286.4</v>
+        <v>14.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14598,12 +14598,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>Living Periphery</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14624,7 +14624,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>264.7</v>
+        <v>631.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Equality in Decision-Making and Power for Women</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>259.5</v>
+        <v>18</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
+          <t>Black Youth Alive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>337.8</v>
+        <v>12.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>230.2</v>
+        <v>76</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>223.3</v>
+        <v>27.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -14773,12 +14773,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>222.5</v>
+        <v>18.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>215.9</v>
+        <v>20.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1905.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -14878,12 +14878,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>213.3</v>
+        <v>87</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14939,7 +14939,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>163.9</v>
+        <v>800.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
+          <t>Basic Education Democratic, with Quality and Equity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>143</v>
+        <v>68424.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Better Cities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>139.8</v>
+        <v>16875</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Communications for Inclusion and Transformation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>136</v>
+        <v>2102.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -15053,12 +15053,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+          <t>Cooperation of Defence for National Development</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>135.5</v>
+        <v>1054.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -15088,12 +15088,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>135.2</v>
+        <v>478</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Electric Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15184,7 +15184,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>108.1</v>
+        <v>143</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+          <t>Family Farming and Agroecology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>90.40000000000001</v>
+        <v>7781</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>87</v>
+        <v>108.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -15263,12 +15263,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Institutional Security</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -15298,12 +15298,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>66.90000000000001</v>
+        <v>1125</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
+          <t>National Defense</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>467.3</v>
+        <v>13846.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -15368,12 +15368,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
+          <t>Ocean, Coastal Zone and Antarctica</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>74.3</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>48.8</v>
+        <v>264.7</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>45</v>
+        <v>42.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -15473,12 +15473,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
+          <t>Primary Health Care</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>42.1</v>
+        <v>51241.7</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ocean, Coastal Zone and Antarctica</t>
+          <t>Professional and Technological Education that Transforms</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>50.4</v>
+        <v>4085.3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>30.8</v>
+        <v>337.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
+          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>28</v>
+        <v>158.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -15613,12 +15613,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15639,7 +15639,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.2</v>
+        <v>34.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15674,7 +15674,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>34.8</v>
+        <v>800.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+          <t>Public Security with Citizenship</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>20.1</v>
+        <v>5354.6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
+          <t>Rail Transport</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -15744,7 +15744,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>18.1</v>
+        <v>1104.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -15753,12 +15753,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equality in Decision-Making and Power for Women</t>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>18</v>
+        <v>74.3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Climate Emergency Response</t>
+          <t>Right to Culture</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -15814,7 +15814,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10497.6</v>
+        <v>2026.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -15823,12 +15823,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Structuring the National Care Policy</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>14.9</v>
+        <v>222.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Black Youth Alive</t>
+          <t>Risk and Disaster Management</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.4</v>
+        <v>1905.3</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -15893,12 +15893,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Water Resources: Water in Quantity and Quality Forever</t>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2176.2</v>
+        <v>6801</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Basic Sanitation</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15954,7 +15954,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2895.5</v>
+        <v>6472.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -15963,12 +15963,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15989,7 +15989,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>800.8</v>
+        <v>886652.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16024,7 +16024,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>800.8</v>
+        <v>28</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Public Security with Citizenship</t>
+          <t>State Transformation for Citizenship and Development</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5354.6</v>
+        <v>286.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -16068,12 +16068,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
+          <t>Supply and Food Sovereignty</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -16094,7 +16094,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>14463.9</v>
+        <v>23058</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Living Periphery</t>
+          <t>Sustainable Fisheries and Aquaculture</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16129,7 +16129,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>631.2</v>
+        <v>215.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -16138,12 +16138,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
+          <t>Water Resources: Water in Quantity and Quality Forever</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16164,7 +16164,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>158.2</v>
+        <v>2176.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -16173,12 +16173,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sustainable Agriculture</t>
+          <t>Women Living Free from Violence</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>14910.1</v>
+        <v>230.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>

--- a/UNION_PANEL.xlsx
+++ b/UNION_PANEL.xlsx
@@ -519,27 +519,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sustainable Agriculture</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,27 +547,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>14910.1</v>
+        <v>169512</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>14910.1</v>
+        <v>169512</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -588,22 +580,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -616,19 +608,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>22632</v>
+        <v>103391.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>22632</v>
+        <v>103391.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -649,27 +649,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Climate Emergency Response</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -692,12 +692,12 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>10497.6</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>10497.6</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -718,22 +718,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>30.8</v>
+        <v>78582.2</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>30.8</v>
+        <v>78582.2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -856,17 +856,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -886,12 +882,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Demographic Shifts</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -899,12 +895,12 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>135.5</v>
+        <v>886652.4</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>135.5</v>
+        <v>886652.4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -925,22 +921,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2224</t>
-        </is>
-      </c>
+          <t>Basic Education Democratic, with Quality and Equity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -960,7 +952,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Demographic Shifts; Pandemics; Technological Change</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -968,12 +960,12 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>136</v>
+        <v>68424.8</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>136</v>
+        <v>68424.8</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -994,22 +986,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
+          <t>Primary Health Care</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1029,7 +1017,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1037,12 +1025,12 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>286.4</v>
+        <v>51241.7</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>286.4</v>
+        <v>51241.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1063,27 +1051,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1091,27 +1079,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>213.3</v>
+        <v>27428.4</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>213.3</v>
+        <v>27428.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1132,22 +1112,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1160,27 +1140,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>399.2</v>
+        <v>22632</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>399.2</v>
+        <v>22632</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1201,22 +1173,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1244,12 +1216,12 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>467.3</v>
+        <v>15913.4</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>467.3</v>
+        <v>15913.4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1270,22 +1242,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2307</t>
-        </is>
-      </c>
+          <t>Better Cities</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Urban Development</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1300,25 +1268,25 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>150.7</v>
+        <v>16875</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>150.7</v>
+        <v>16875</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1339,42 +1307,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
+          <t>National Defense</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Democratic Backsliding; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1382,12 +1346,12 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>6183</v>
+        <v>13846.4</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>6183</v>
+        <v>13846.4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1408,27 +1372,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1443,7 +1407,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1451,12 +1415,12 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>78582.2</v>
+        <v>13474.9</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>78582.2</v>
+        <v>13474.9</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1477,27 +1441,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1507,12 +1471,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1520,12 +1484,12 @@
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>259.5</v>
+        <v>13130.8</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>259.5</v>
+        <v>13130.8</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1546,22 +1510,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1574,19 +1538,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>6546.1</v>
+        <v>12297.7</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>6546.1</v>
+        <v>12297.7</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1607,12 +1579,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1622,12 +1594,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1614,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1650,12 +1622,12 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>3396.6</v>
+        <v>8397</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>3396.6</v>
+        <v>8397</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1676,22 +1648,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
+          <t>Science, technology and innovation for social development</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1711,20 +1679,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>12297.7</v>
+        <v>6472.2</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>12297.7</v>
+        <v>6472.2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1745,27 +1713,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Basic Sanitation</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1773,27 +1737,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>2895.5</v>
+        <v>6801</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>2895.5</v>
+        <v>6801</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1814,27 +1770,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1842,19 +1798,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>2557.2</v>
+        <v>6183</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>2557.2</v>
+        <v>6183</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1875,22 +1839,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1905,12 +1869,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1918,12 +1882,12 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>1870.2</v>
+        <v>4810.6</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1870.2</v>
+        <v>4810.6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1944,22 +1908,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
+          <t>Professional and Technological Education that Transforms</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1974,12 +1934,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1987,12 +1947,12 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>1870.2</v>
+        <v>4085.3</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1870.2</v>
+        <v>4085.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2013,22 +1973,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2048,7 +2008,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2056,12 +2016,12 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>139.8</v>
+        <v>4015.2</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>139.8</v>
+        <v>4015.2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2082,27 +2042,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2112,12 +2072,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2125,12 +2085,12 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>66.90000000000001</v>
+        <v>3396.6</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>66.90000000000001</v>
+        <v>3396.6</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2151,27 +2111,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Indigenous Health</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2179,27 +2139,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>557.9</v>
+        <v>2584.2</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>557.9</v>
+        <v>2584.2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2220,17 +2172,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>Tourism, This Is the Destination</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2248,27 +2200,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>8397</v>
+        <v>2557.2</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>8397</v>
+        <v>2557.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2289,27 +2233,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2317,27 +2261,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>13130.8</v>
+        <v>6546.1</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>13130.8</v>
+        <v>6546.1</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2358,27 +2294,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Road Safety</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>3108</t>
-        </is>
-      </c>
+          <t>Communications for Inclusion and Transformation</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2401,12 +2333,12 @@
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>328.8</v>
+        <v>2102.4</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>328.8</v>
+        <v>2102.4</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2427,22 +2359,18 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sustainable Popular and Solidarity Economy</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>4006</t>
-        </is>
-      </c>
+          <t>Right to Culture</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2458,14 +2386,16 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>2026.6</v>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2026.6</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2486,22 +2416,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Public and Government Communication</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2514,25 +2444,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>2000</v>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2553,22 +2477,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2583,12 +2507,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2596,12 +2520,12 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>163.9</v>
+        <v>1870.2</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>163.9</v>
+        <v>1870.2</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2622,22 +2546,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2657,7 +2581,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2665,12 +2589,12 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>135.2</v>
+        <v>1870.2</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>135.2</v>
+        <v>1870.2</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2691,27 +2615,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2726,7 +2646,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Technological Change</t>
+          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2734,12 +2654,12 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>14463.9</v>
+        <v>1125</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>14463.9</v>
+        <v>1125</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2760,27 +2680,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>5117</t>
-        </is>
-      </c>
+          <t>Rail Transport</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2795,12 +2711,12 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>27428.4</v>
+        <v>1104.2</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>27428.4</v>
+        <v>1104.2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2821,27 +2737,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
+          <t>Cooperation of Defence for National Development</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2849,27 +2761,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Pandemics</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>93847.39999999999</v>
+        <v>1054.1</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>93847.39999999999</v>
+        <v>1054.1</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2890,22 +2794,18 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>5120</t>
-        </is>
-      </c>
+          <t>Supply and Food Sovereignty</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2925,20 +2825,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>4015.2</v>
+        <v>23058</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>4015.2</v>
+        <v>23058</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2959,22 +2859,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2994,7 +2894,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3002,12 +2902,12 @@
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>15913.4</v>
+        <v>150.7</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>15913.4</v>
+        <v>150.7</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3028,22 +2928,18 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>5122</t>
-        </is>
-      </c>
+          <t>Family Farming and Agroecology</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3056,19 +2952,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>2584.2</v>
+        <v>7781</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>2584.2</v>
+        <v>7781</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3089,27 +2993,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3117,27 +3021,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>13474.9</v>
+        <v>592.4</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>13474.9</v>
+        <v>592.4</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3158,22 +3054,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3186,19 +3082,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>2000</v>
+        <v>557.9</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>2000</v>
+        <v>557.9</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3219,27 +3123,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3247,19 +3147,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding; Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>169512</v>
+        <v>478</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>169512</v>
+        <v>478</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3280,22 +3188,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3310,12 +3218,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3323,12 +3231,12 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>103391.9</v>
+        <v>399.2</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>103391.9</v>
+        <v>399.2</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3349,27 +3257,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Road Safety</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3379,12 +3287,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3392,12 +3300,12 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>4810.6</v>
+        <v>328.8</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>4810.6</v>
+        <v>328.8</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3418,27 +3326,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
+          <t>State Transformation for Citizenship and Development</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3446,19 +3350,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>223.3</v>
+        <v>286.4</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>223.3</v>
+        <v>286.4</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3479,27 +3391,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3507,19 +3419,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K46" t="n">
         <v>1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>48.8</v>
+        <v>286.4</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>48.8</v>
+        <v>286.4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3540,17 +3460,13 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3571,16 +3487,16 @@
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>592.4</v>
+        <v>264.7</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>592.4</v>
+        <v>264.7</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3601,22 +3517,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Structuring the National Care Policy</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3629,19 +3545,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K48" t="n">
         <v>1</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>14.9</v>
+        <v>259.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>14.9</v>
+        <v>259.5</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3662,22 +3586,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Living Periphery</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>5602</t>
-        </is>
-      </c>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Urban Development</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3690,19 +3610,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
       <c r="K49" t="n">
         <v>1</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>631.2</v>
+        <v>337.8</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>631.2</v>
+        <v>337.8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3723,17 +3651,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Equality in Decision-Making and Power for Women</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>5661</t>
-        </is>
-      </c>
+          <t>Women Living Free from Violence</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3758,7 +3682,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3766,12 +3690,12 @@
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>230.2</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>18</v>
+        <v>230.2</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3792,27 +3716,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Black Youth Alive</t>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3820,27 +3744,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
         <v>1</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>12.4</v>
+        <v>223.3</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>12.4</v>
+        <v>223.3</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3861,17 +3777,13 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
+          <t>Rights and Participation of Indigenous Peoples</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3889,27 +3801,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>76</v>
+        <v>222.5</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>76</v>
+        <v>222.5</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3930,27 +3834,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
+          <t>Sustainable Fisheries and Aquaculture</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3958,19 +3858,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>27.2</v>
+        <v>215.9</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>27.2</v>
+        <v>215.9</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3991,27 +3899,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
+          <t>Risk and Disaster Management</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4019,19 +3923,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>18.1</v>
+        <v>1905.3</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>18.1</v>
+        <v>1905.3</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -4052,22 +3964,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4087,7 +3999,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Demographic Shifts</t>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -4095,12 +4007,12 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>20.1</v>
+        <v>213.3</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>20.1</v>
+        <v>213.3</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4121,22 +4033,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4146,7 +4058,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4156,7 +4068,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4164,12 +4076,12 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>90.40000000000001</v>
+        <v>163.9</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>90.40000000000001</v>
+        <v>163.9</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4190,27 +4102,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
+          <t>Electric Energy</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4218,19 +4126,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Climate Change; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4251,22 +4167,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4281,12 +4197,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4294,12 +4210,12 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>800.8</v>
+        <v>139.8</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>800.8</v>
+        <v>139.8</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4320,18 +4236,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Planning and Budgeting for Sustainable Development</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4351,7 +4271,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Pandemics; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -4359,12 +4279,12 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>68424.8</v>
+        <v>136</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>68424.8</v>
+        <v>136</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4385,18 +4305,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Better Cities</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1617</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Urban Development</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4416,20 +4340,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>16875</v>
+        <v>135.5</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>16875</v>
+        <v>135.5</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4450,18 +4374,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Transparency, Integrity and Anti-Corruption</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4481,7 +4409,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4489,12 +4417,12 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>2102.4</v>
+        <v>135.2</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>2102.4</v>
+        <v>135.2</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4515,23 +4443,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
+          <t>Economic Autonomy of Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4539,19 +4467,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>1054.1</v>
+        <v>122.3</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>1054.1</v>
+        <v>122.3</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4572,23 +4508,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4596,27 +4532,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
         <v>1</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>478</v>
+        <v>108.1</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>478</v>
+        <v>108.1</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4637,10 +4565,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>5816</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -4658,17 +4590,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -4676,12 +4608,12 @@
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>122.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>122.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4702,23 +4634,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>5838</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4726,27 +4662,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Climate Change; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4767,18 +4695,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>5804</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4793,12 +4725,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -4806,12 +4738,12 @@
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>7781</v>
+        <v>76</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>7781</v>
+        <v>76</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4832,18 +4764,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4856,19 +4792,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>108.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>108.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4889,23 +4833,27 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Nuclear Policy</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2306</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4920,7 +4868,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4928,12 +4876,12 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>45</v>
+        <v>467.3</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>45</v>
+        <v>467.3</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4954,7 +4902,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -4965,12 +4913,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4980,12 +4928,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
+          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4993,12 +4941,12 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>1125</v>
+        <v>74.3</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>1125</v>
+        <v>74.3</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -5019,51 +4967,47 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>National Defense</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Youth: Rights, Participation and Good Living</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Shifts in Globalisation</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>13846.4</v>
+        <v>48.8</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>13846.4</v>
+        <v>48.8</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5084,23 +5028,23 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ocean, Coastal Zone and Antarctica</t>
+          <t>Institutional Security</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5110,12 +5054,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5123,12 +5067,12 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>50.4</v>
+        <v>45</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>50.4</v>
+        <v>45</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5149,13 +5093,13 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5173,19 +5117,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>264.7</v>
+        <v>42.1</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>264.7</v>
+        <v>42.1</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5206,18 +5158,18 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
+          <t>Ocean, Coastal Zone and Antarctica</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5237,7 +5189,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5245,12 +5197,12 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>42.1</v>
+        <v>50.4</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>42.1</v>
+        <v>50.4</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5271,23 +5223,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Environmental Quality in Cities and the Countryside</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5297,12 +5253,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -5310,12 +5266,12 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>51241.7</v>
+        <v>30.8</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>51241.7</v>
+        <v>30.8</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5336,23 +5292,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5360,27 +5316,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Increased Polarisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>4085.3</v>
+        <v>28</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>4085.3</v>
+        <v>28</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5401,18 +5349,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>5812</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5425,27 +5377,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>337.8</v>
+        <v>27.2</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>337.8</v>
+        <v>27.2</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5466,18 +5410,18 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5497,7 +5441,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -5505,12 +5449,12 @@
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>158.2</v>
+        <v>34.8</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>158.2</v>
+        <v>34.8</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5531,10 +5475,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -5542,12 +5490,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5562,7 +5510,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Demographic Shifts</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -5570,12 +5518,12 @@
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>34.8</v>
+        <v>20.1</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>34.8</v>
+        <v>20.1</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -5596,18 +5544,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>5814</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5620,27 +5572,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="n">
-        <v>800.8</v>
+        <v>18.1</v>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
-        <v>800.8</v>
+        <v>18.1</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -5661,10 +5605,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Public Security with Citizenship</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Equality in Decision-Making and Power for Women</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>5661</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -5672,12 +5620,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5687,12 +5635,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Technological Change</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K80" t="n">
@@ -5700,12 +5648,12 @@
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="n">
-        <v>5354.6</v>
+        <v>18</v>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="n">
-        <v>5354.6</v>
+        <v>18</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -5726,18 +5674,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Climate Emergency Response</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1158</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5750,19 +5702,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="n">
-        <v>1104.2</v>
+        <v>10497.6</v>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
-        <v>1104.2</v>
+        <v>10497.6</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -5783,18 +5743,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Structuring the National Care Policy</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>5501</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5807,27 +5771,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="n">
-        <v>74.3</v>
+        <v>14.9</v>
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
-        <v>74.3</v>
+        <v>14.9</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -5848,18 +5804,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Black Youth Alive</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>5803</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5872,19 +5832,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="n">
-        <v>2026.6</v>
+        <v>12.4</v>
       </c>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
-        <v>2026.6</v>
+        <v>12.4</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -5905,23 +5873,23 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>Water Resources: Water in Quantity and Quality Forever</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5929,19 +5897,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="n">
-        <v>222.5</v>
+        <v>2176.2</v>
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
-        <v>222.5</v>
+        <v>2176.2</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -5962,23 +5938,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Basic Sanitation</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2322</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5993,7 +5973,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -6001,12 +5981,12 @@
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="n">
-        <v>1905.3</v>
+        <v>2895.5</v>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="n">
-        <v>1905.3</v>
+        <v>2895.5</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6027,23 +6007,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6051,19 +6035,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="n">
-        <v>6801</v>
+        <v>800.8</v>
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="n">
-        <v>6801</v>
+        <v>800.8</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6084,18 +6076,18 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6110,25 +6102,25 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>6472.2</v>
+        <v>800.8</v>
       </c>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
-        <v>6472.2</v>
+        <v>800.8</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6149,18 +6141,18 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
+          <t>Public Security with Citizenship</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6175,12 +6167,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Demographic Shifts</t>
+          <t>Biodiversity Loss; Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -6188,12 +6180,12 @@
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="n">
-        <v>886652.4</v>
+        <v>5354.6</v>
       </c>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>886652.4</v>
+        <v>5354.6</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -6214,23 +6206,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>5113</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6238,19 +6234,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Demographic Shifts; Technological Change</t>
+        </is>
+      </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="n">
-        <v>28</v>
+        <v>14463.9</v>
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
-        <v>28</v>
+        <v>14463.9</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -6271,18 +6275,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Living Periphery</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Urban Development</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6295,27 +6303,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="n">
         <v>1</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="n">
-        <v>286.4</v>
+        <v>631.2</v>
       </c>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
-        <v>286.4</v>
+        <v>631.2</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
@@ -6336,18 +6336,18 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
+          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6367,20 +6367,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="n">
-        <v>23058</v>
+        <v>158.2</v>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
-        <v>23058</v>
+        <v>158.2</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -6401,10 +6401,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Sustainable Agriculture</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>Agriculture</t>
@@ -6427,12 +6431,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -6440,12 +6444,12 @@
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="n">
-        <v>215.9</v>
+        <v>14910.1</v>
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="n">
-        <v>215.9</v>
+        <v>14910.1</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
@@ -6466,18 +6470,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Water Resources: Water in Quantity and Quality Forever</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Public and Government Communication</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6492,25 +6500,23 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="n">
-        <v>2176.2</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
-        <v>2176.2</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -6531,18 +6537,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Sustainable Popular and Solidarity Economy</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6555,27 +6565,17 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="n">
-        <v>230.2</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="n">
-        <v>230.2</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sustainable Agriculture</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14910.1</v>
+        <v>169512</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13058,12 +13058,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22632</v>
+        <v>103391.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Climate Emergency Response</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10497.6</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>78582.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>135.5</v>
+        <v>886652.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Basic Education Democratic, with Quality and Equity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>136</v>
+        <v>68424.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>Primary Health Care</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>286.4</v>
+        <v>51241.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>213.3</v>
+        <v>27428.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -13338,12 +13338,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>399.2</v>
+        <v>22632</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>467.3</v>
+        <v>15913.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Better Cities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>150.7</v>
+        <v>16875</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>National Defense</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6183</v>
+        <v>13846.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -13478,12 +13478,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>78582.2</v>
+        <v>13474.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>259.5</v>
+        <v>13130.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6546.1</v>
+        <v>12297.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3396.6</v>
+        <v>8397</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13644,7 +13644,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12297.7</v>
+        <v>6472.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Basic Sanitation</t>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2895.5</v>
+        <v>6801</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -13688,12 +13688,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2557.2</v>
+        <v>6183</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1870.2</v>
+        <v>4810.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+          <t>Professional and Technological Education that Transforms</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1870.2</v>
+        <v>4085.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>139.8</v>
+        <v>4015.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66.90000000000001</v>
+        <v>3396.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -13863,12 +13863,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13880,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Indigenous Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>557.9</v>
+        <v>2584.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>Tourism, This Is the Destination</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8397</v>
+        <v>2557.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13959,7 +13959,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13130.8</v>
+        <v>6546.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -13968,12 +13968,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>Communications for Inclusion and Transformation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13994,7 +13994,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>328.8</v>
+        <v>2102.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -14003,12 +14003,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Right to Culture</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14029,7 +14029,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>163.9</v>
+        <v>2026.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>135.2</v>
+        <v>2000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -14073,12 +14073,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14463.9</v>
+        <v>1870.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27428.4</v>
+        <v>1870.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14169,7 +14169,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>93847.39999999999</v>
+        <v>1125</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+          <t>Rail Transport</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4015.2</v>
+        <v>1104.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -14213,12 +14213,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
+          <t>Cooperation of Defence for National Development</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15913.4</v>
+        <v>1054.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14265,7 +14265,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
+          <t>Supply and Food Sovereignty</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2584.2</v>
+        <v>23058</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13474.9</v>
+        <v>150.7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Family Farming and Agroecology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2000</v>
+        <v>7781</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14379,7 +14379,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>169512</v>
+        <v>592.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>103391.9</v>
+        <v>557.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -14423,12 +14423,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14449,7 +14449,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4810.6</v>
+        <v>478</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>223.3</v>
+        <v>399.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -14493,12 +14493,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
+          <t>Road Safety</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>48.8</v>
+        <v>328.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+          <t>State Transformation for Citizenship and Development</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>592.4</v>
+        <v>286.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Structuring the National Care Policy</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.9</v>
+        <v>286.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14598,12 +14598,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Living Periphery</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14624,7 +14624,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>631.2</v>
+        <v>264.7</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equality in Decision-Making and Power for Women</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>259.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Black Youth Alive</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.4</v>
+        <v>337.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Women Living Free from Violence</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>76</v>
+        <v>230.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27.2</v>
+        <v>223.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -14773,12 +14773,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18.1</v>
+        <v>222.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+          <t>Sustainable Fisheries and Aquaculture</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>20.1</v>
+        <v>215.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+          <t>Risk and Disaster Management</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>90.40000000000001</v>
+        <v>1905.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -14878,12 +14878,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>87</v>
+        <v>213.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14939,7 +14939,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>800.8</v>
+        <v>163.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
+          <t>Electric Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>68424.8</v>
+        <v>143</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Better Cities</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16875</v>
+        <v>139.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -15035,7 +15035,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
+          <t>Planning and Budgeting for Sustainable Development</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2102.4</v>
+        <v>136</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -15053,12 +15053,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1054.1</v>
+        <v>135.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -15088,12 +15088,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>478</v>
+        <v>135.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15184,7 +15184,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>143</v>
+        <v>108.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7781</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>108.1</v>
+        <v>87</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -15263,12 +15263,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -15298,12 +15298,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1125</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>National Defense</t>
+          <t>Nuclear Policy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13846.4</v>
+        <v>467.3</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -15368,12 +15368,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15385,7 +15385,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ocean, Coastal Zone and Antarctica</t>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>74.3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>Youth: Rights, Participation and Good Living</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>264.7</v>
+        <v>48.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
+          <t>Institutional Security</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>42.1</v>
+        <v>45</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -15473,12 +15473,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>51241.7</v>
+        <v>42.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Ocean, Coastal Zone and Antarctica</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4085.3</v>
+        <v>50.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
+          <t>Environmental Quality in Cities and the Countryside</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>337.8</v>
+        <v>30.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>158.2</v>
+        <v>28</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -15613,12 +15613,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15639,7 +15639,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>34.8</v>
+        <v>27.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15674,7 +15674,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>800.8</v>
+        <v>34.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Public Security with Citizenship</t>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5354.6</v>
+        <v>20.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -15744,7 +15744,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1104.2</v>
+        <v>18.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -15753,12 +15753,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
+          <t>Equality in Decision-Making and Power for Women</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -15779,7 +15779,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>74.3</v>
+        <v>18</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -15805,7 +15805,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
+          <t>Climate Emergency Response</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -15814,7 +15814,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2026.6</v>
+        <v>10497.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -15823,12 +15823,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>Structuring the National Care Policy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>222.5</v>
+        <v>14.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
+          <t>Black Youth Alive</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1905.3</v>
+        <v>12.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -15893,12 +15893,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+          <t>Water Resources: Water in Quantity and Quality Forever</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>6801</v>
+        <v>2176.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Basic Sanitation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -15954,7 +15954,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6472.2</v>
+        <v>2895.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -15963,12 +15963,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -15989,7 +15989,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>886652.4</v>
+        <v>800.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
+          <t>Protection and Recovery of Biodiversity and Combating Deforestation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -16024,7 +16024,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28</v>
+        <v>800.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16050,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
+          <t>Public Security with Citizenship</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>286.4</v>
+        <v>5354.6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -16068,12 +16068,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
+          <t>Higher Education: Quality, Democracy, Equity and Sustainability</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -16094,7 +16094,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>23058</v>
+        <v>14463.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
+          <t>Living Periphery</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -16129,7 +16129,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>215.9</v>
+        <v>631.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -16138,12 +16138,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Water Resources: Water in Quantity and Quality Forever</t>
+          <t>Promotion of Citizenship, Human Rights Protection and Reparation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -16164,7 +16164,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2176.2</v>
+        <v>158.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -16173,12 +16173,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Sustainable Agriculture</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -16199,7 +16199,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>230.2</v>
+        <v>14910.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>

--- a/UNION_PANEL.xlsx
+++ b/UNION_PANEL.xlsx
@@ -519,23 +519,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -550,7 +554,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -558,12 +562,12 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>122.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>122.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -584,18 +588,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Health and Environment Surveillance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -615,7 +623,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Demographic Shifts</t>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -623,12 +631,12 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>886652.4</v>
+        <v>13474.9</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>886652.4</v>
+        <v>13474.9</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -649,14 +657,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -664,12 +668,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -677,19 +681,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Demographic Shifts</t>
+        </is>
+      </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -710,12 +722,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -725,12 +737,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -738,27 +750,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -779,22 +783,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -814,7 +818,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -822,12 +826,12 @@
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -848,22 +852,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -891,12 +895,12 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -917,22 +921,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Environmental Education</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -947,25 +951,25 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -986,10 +990,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Environmental Education</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Education</t>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1012,25 +1020,25 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Pandemics; Technological Change</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1051,13 +1059,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
+          <t>Basic Education Democratic, with Quality and Equity</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1082,7 +1090,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Demographic Shifts; Pandemics; Technological Change</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1090,12 +1098,12 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>51241.7</v>
+        <v>68424.8</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>51241.7</v>
+        <v>68424.8</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1116,27 +1124,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
+          <t>Primary Health Care</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1151,7 +1155,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1159,12 +1163,12 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>135.2</v>
+        <v>51241.7</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>135.2</v>
+        <v>51241.7</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1506,22 +1510,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1541,7 +1545,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1549,12 +1553,12 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>13474.9</v>
+        <v>13130.8</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>13474.9</v>
+        <v>13130.8</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1575,27 +1579,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1618,12 +1622,12 @@
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>13130.8</v>
+        <v>12297.7</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>13130.8</v>
+        <v>12297.7</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1644,27 +1648,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1674,12 +1678,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1687,12 +1691,12 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>12297.7</v>
+        <v>8397</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>12297.7</v>
+        <v>8397</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1713,27 +1717,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
+          <t>Science, technology and innovation for social development</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1743,25 +1743,25 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>8397</v>
+        <v>6472.2</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>8397</v>
+        <v>6472.2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1782,13 +1782,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1806,27 +1806,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>6472.2</v>
+        <v>6801</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>6472.2</v>
+        <v>6801</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1847,10 +1839,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Industry</t>
@@ -1863,7 +1859,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1871,19 +1867,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>6801</v>
+        <v>6183</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>6801</v>
+        <v>6183</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1904,22 +1908,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
+          <t>Professional and Technological Education that Transforms</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>6183</v>
+        <v>4085.3</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>6183</v>
+        <v>4085.3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1973,23 +1973,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Civil Aviation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3104</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2004,7 +2008,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2012,12 +2016,12 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>4085.3</v>
+        <v>557.9</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>4085.3</v>
+        <v>557.9</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2542,22 +2546,18 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
+          <t>Family Farming and Agroecology</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>1870.2</v>
+        <v>7781</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1870.2</v>
+        <v>7781</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2611,12 +2611,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2680,13 +2680,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Innovation in Enterprises for a New Industrialization</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2696,7 +2700,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2711,7 +2715,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2719,12 +2723,12 @@
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>215.9</v>
+        <v>1870.2</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>215.9</v>
+        <v>1870.2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2989,10 +2993,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5136</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Agriculture</t>
@@ -3000,7 +3008,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3013,27 +3021,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>7781</v>
+        <v>592.4</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>7781</v>
+        <v>592.4</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3054,22 +3054,18 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3082,19 +3078,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding; Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>592.4</v>
+        <v>478</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>592.4</v>
+        <v>478</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3115,27 +3119,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3145,12 +3149,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -3158,12 +3162,12 @@
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>557.9</v>
+        <v>399.2</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>557.9</v>
+        <v>399.2</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3184,23 +3188,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Road Safety</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3108</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3215,7 +3223,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3223,12 +3231,12 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>478</v>
+        <v>328.8</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>478</v>
+        <v>328.8</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3249,22 +3257,18 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
+          <t>State Transformation for Citizenship and Development</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3279,12 +3283,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3292,12 +3296,12 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>399.2</v>
+        <v>286.4</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>399.2</v>
+        <v>286.4</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3318,22 +3322,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3361,12 +3365,12 @@
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="n">
-        <v>328.8</v>
+        <v>286.4</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>328.8</v>
+        <v>286.4</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3387,7 +3391,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -3398,7 +3402,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3411,27 +3415,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>286.4</v>
+        <v>264.7</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>286.4</v>
+        <v>264.7</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3452,27 +3448,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3482,12 +3478,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3495,12 +3491,12 @@
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>286.4</v>
+        <v>259.5</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>286.4</v>
+        <v>259.5</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3521,7 +3517,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -3532,7 +3528,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3545,19 +3541,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>264.7</v>
+        <v>337.8</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>264.7</v>
+        <v>337.8</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3578,22 +3582,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2315</t>
-        </is>
-      </c>
+          <t>Women Living Free from Violence</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>259.5</v>
+        <v>230.2</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>259.5</v>
+        <v>230.2</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3647,23 +3647,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3671,27 +3675,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>337.8</v>
+        <v>223.3</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>337.8</v>
+        <v>223.3</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3712,13 +3708,13 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3736,27 +3732,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>230.2</v>
+        <v>222.5</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>230.2</v>
+        <v>222.5</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3777,27 +3765,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
+          <t>Sustainable Fisheries and Aquaculture</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3805,19 +3789,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>223.3</v>
+        <v>215.9</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>223.3</v>
+        <v>215.9</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3838,7 +3830,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>Risk and Disaster Management</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -3849,12 +3841,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3862,19 +3854,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>222.5</v>
+        <v>1905.3</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>222.5</v>
+        <v>1905.3</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3895,18 +3895,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Agricultural Defense</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3919,19 +3923,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
+        </is>
+      </c>
       <c r="K54" t="n">
         <v>1</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>108.1</v>
+        <v>213.3</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>108.1</v>
+        <v>213.3</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3952,23 +3964,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Financial System of the Future</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3978,12 +3994,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3991,12 +4007,12 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>1905.3</v>
+        <v>163.9</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>1905.3</v>
+        <v>163.9</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4017,27 +4033,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4047,12 +4063,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4060,12 +4076,12 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>213.3</v>
+        <v>4810.6</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>213.3</v>
+        <v>4810.6</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4086,22 +4102,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>2307</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4129,12 +4145,12 @@
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>163.9</v>
+        <v>150.7</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>163.9</v>
+        <v>150.7</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4155,27 +4171,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>5133</t>
-        </is>
-      </c>
+          <t>Electric Energy</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4190,7 +4202,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Climate Change; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4198,12 +4210,12 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>4810.6</v>
+        <v>143</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>4810.6</v>
+        <v>143</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4224,22 +4236,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4259,7 +4271,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -4267,12 +4279,12 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>150.7</v>
+        <v>139.8</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>150.7</v>
+        <v>139.8</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4293,18 +4305,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Planning and Budgeting for Sustainable Development</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2224</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4319,12 +4335,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Climate Change; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -4332,12 +4348,12 @@
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4358,22 +4374,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4388,12 +4404,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4401,12 +4417,12 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>139.8</v>
+        <v>135.5</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>139.8</v>
+        <v>135.5</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4427,12 +4443,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4442,12 +4458,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4462,7 +4478,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4470,12 +4486,12 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>136</v>
+        <v>135.2</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>136</v>
+        <v>135.2</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4496,17 +4512,13 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1617</t>
-        </is>
-      </c>
+          <t>Economic Autonomy of Women</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4526,12 +4538,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4539,12 +4551,12 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>135.5</v>
+        <v>122.3</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>135.5</v>
+        <v>122.3</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4565,14 +4577,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -4580,40 +4588,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4634,12 +4634,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4659,22 +4659,30 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4695,12 +4703,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4723,27 +4731,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4764,27 +4764,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>66.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>66.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Religious education and youth spiritual development</t>
+          <t>National Education System Strengthening</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -6612,7 +6612,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6620,17 +6620,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Shifts in Globalisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>599.2</v>
+      </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>599.2</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6651,23 +6661,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Unfunded social cohesion and civic participation strategy</t>
+          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6677,23 +6687,25 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Biodiversity Loss; Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>472.3</v>
+      </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>472.3</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6714,23 +6726,23 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>National Education System Strengthening</t>
+          <t>Electricity supply projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6745,20 +6757,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>599.2</v>
+        <v>400</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>599.2</v>
+        <v>400</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6779,23 +6791,23 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
+          <t>National housing provision projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6803,19 +6815,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K98" t="n">
         <v>1</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>150</v>
+        <v>277</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>150</v>
+        <v>277</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6836,18 +6856,18 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
+          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6867,7 +6887,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Shifts in Globalisation; Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -6876,11 +6896,11 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>472.3</v>
+        <v>261.1</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
-        <v>472.3</v>
+        <v>261.1</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6901,18 +6921,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Electricity supply projects under the 12th National Development Plan</t>
+          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6922,17 +6942,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6941,11 +6961,11 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>400</v>
+        <v>256.5</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
-        <v>400</v>
+        <v>256.5</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6966,23 +6986,23 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>National housing provision projects under the 12th National Development Plan</t>
+          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6990,27 +7010,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>277</v>
+        <v>150</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
-        <v>277</v>
+        <v>150</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7031,18 +7043,18 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
+          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7062,7 +7074,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -7071,11 +7083,11 @@
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>261.1</v>
+        <v>144.7</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>261.1</v>
+        <v>144.7</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7096,18 +7108,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
+          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7117,30 +7129,30 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>256.5</v>
+        <v>126.6</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>256.5</v>
+        <v>126.6</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -7161,23 +7173,23 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
+          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7185,27 +7197,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
-        <v>144.7</v>
+        <v>89</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>144.7</v>
+        <v>89</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -7226,7 +7230,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
+          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -7257,20 +7261,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Pandemics</t>
+          <t>Resource and Energy Pressures; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>126.6</v>
+        <v>80</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>126.6</v>
+        <v>80</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -7291,23 +7295,23 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
+          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7315,19 +7319,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="n">
-        <v>89</v>
+        <v>68.3</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
-        <v>89</v>
+        <v>68.3</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -7348,18 +7360,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
+          <t>Flood prevention projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7379,7 +7391,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Shifts in Globalisation</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -7388,11 +7400,11 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
-        <v>80</v>
+        <v>62.5</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -7413,23 +7425,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
+          <t>Bru-HIMS 2.0 system project</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7444,7 +7456,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -7453,11 +7465,11 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
-        <v>68.3</v>
+        <v>62.5</v>
       </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
-        <v>68.3</v>
+        <v>62.5</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -7478,18 +7490,18 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Flood prevention projects under the 12th National Development Plan</t>
+          <t>Research and innovation allocations under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7509,7 +7521,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -7518,11 +7530,11 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>62.5</v>
+        <v>61.8</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
-        <v>62.5</v>
+        <v>61.8</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -7543,23 +7555,23 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bru-HIMS 2.0 system project</t>
+          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7574,7 +7586,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Democratic Backsliding; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -7583,11 +7595,11 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -7608,23 +7620,23 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Research and innovation allocations under the 12th National Development Plan</t>
+          <t>Green Building initiatives under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7639,7 +7651,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7648,11 +7660,11 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
-        <v>61.8</v>
+        <v>50</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -7673,18 +7685,18 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
+          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7704,7 +7716,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Resource and Energy Pressures; Technological Change</t>
+          <t>Demographic Shifts; Technological Change</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7713,11 +7725,11 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
-        <v>60</v>
+        <v>37.3</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
-        <v>60</v>
+        <v>37.3</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -7738,28 +7750,28 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Green Building initiatives under the 12th National Development Plan</t>
+          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7769,7 +7781,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Climate Change; Democratic Backsliding; Demographic Shifts; Increased Polarisation; Pandemics</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7778,11 +7790,11 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -7803,23 +7815,23 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
+          <t>Government digital transformation projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7834,7 +7846,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Technological Change</t>
+          <t>Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -7843,11 +7855,11 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="n">
-        <v>37.3</v>
+        <v>36.5</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -7868,18 +7880,18 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
+          <t>Tourism product improvement projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7889,17 +7901,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Demographic Shifts; Increased Polarisation; Pandemics</t>
+          <t>Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -7908,11 +7920,11 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
-        <v>37</v>
+        <v>36.4</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
@@ -7933,23 +7945,23 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Government digital transformation projects under the 12th National Development Plan</t>
+          <t>Education information and data management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7964,7 +7976,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -7973,11 +7985,11 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
-        <v>36.5</v>
+        <v>21.2</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>36.5</v>
+        <v>21.2</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -7998,23 +8010,23 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tourism product improvement projects under the 12th National Development Plan</t>
+          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8022,27 +8034,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Shifts in Globalisation</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="n">
         <v>1</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>36.4</v>
+        <v>19.4</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="n">
-        <v>36.4</v>
+        <v>19.4</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -8518,18 +8522,18 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Education information and data management systems under the 12th National Development Plan</t>
+          <t>Aquaculture industry site development and basic infrastructure projects</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8542,27 +8546,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="n">
         <v>1</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
-        <v>21.2</v>
+        <v>18.5</v>
       </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
-        <v>21.2</v>
+        <v>18.5</v>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
@@ -8583,18 +8579,18 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
+          <t>Livestock industry development plan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8607,19 +8603,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Shifts in Globalisation</t>
+        </is>
+      </c>
       <c r="K126" t="n">
         <v>1</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
@@ -8640,23 +8644,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Aquaculture industry site development and basic infrastructure projects</t>
+          <t>Environmental sustainability, reforestation and forest conservation programmes under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Future Generations</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8664,19 +8668,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K127" t="n">
         <v>1</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -8697,7 +8709,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Livestock industry development plan</t>
+          <t>High-technology vegetable production enhancement programme under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -8713,7 +8725,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8728,7 +8740,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation</t>
+          <t>Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -8737,11 +8749,11 @@
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
-        <v>18.1</v>
+        <v>17.5</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -8762,23 +8774,23 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Environmental sustainability, reforestation and forest conservation programmes under the 12th National Development Plan</t>
+          <t>Digital transformation in the transport and logistics sector under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Future Generations</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8793,7 +8805,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -8802,11 +8814,11 @@
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
-        <v>17.6</v>
+        <v>15.7</v>
       </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="n">
-        <v>17.6</v>
+        <v>15.7</v>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
@@ -8827,28 +8839,28 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>High-technology vegetable production enhancement programme under the 12th National Development Plan</t>
+          <t>Migration from TAFIS 1.0 to TAFIS 2.0</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8858,7 +8870,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -8867,11 +8879,11 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
-        <v>17.5</v>
+        <v>10.8</v>
       </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="n">
-        <v>17.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
@@ -8892,18 +8904,18 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Digital transformation in the transport and logistics sector under the 12th National Development Plan</t>
+          <t>Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8916,27 +8928,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="n">
         <v>1</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="n">
-        <v>15.7</v>
+        <v>10</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -8957,51 +8961,43 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Migration from TAFIS 1.0 to TAFIS 2.0</t>
+          <t>Paddy buy-back scheme and purchase of hybrid paddy seeds</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="n">
         <v>1</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -9022,23 +9018,23 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Preparation and upgrading works for infrastructure and basic facilities in existing and new agricultural development areas</t>
+          <t>Research costs for public higher education institutions</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -9046,19 +9042,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K133" t="n">
         <v>1</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -9079,23 +9083,23 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Paddy buy-back scheme and purchase of hybrid paddy seeds</t>
+          <t>Miftaahun Najaah Scheme</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9103,19 +9107,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K134" t="n">
         <v>1</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -9136,23 +9148,23 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Research costs for public higher education institutions</t>
+          <t>National Adaptation Plan for Climate Change under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9167,7 +9179,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -9176,11 +9188,11 @@
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -9201,23 +9213,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miftaahun Najaah Scheme</t>
+          <t>Construction programme for sewerage and waste drainage infrastructure systems</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9232,20 +9244,18 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
@@ -9266,18 +9276,18 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>National Adaptation Plan for Climate Change under the 12th National Development Plan</t>
+          <t>National security, defence and public safety infrastructure</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9297,20 +9307,18 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
+          <t>Democratic Backsliding; Technological Change</t>
         </is>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="n">
-        <v>1</v>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -9331,13 +9339,13 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Construction programme for sewerage and waste drainage infrastructure systems</t>
+          <t>Public sector performance and welfare data systems</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9357,12 +9365,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -9394,23 +9402,23 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Industrial and business site infrastructure provision</t>
+          <t>National Entrepreneurship Agenda</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9425,7 +9433,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -9457,18 +9465,18 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>National security, defence and public safety infrastructure</t>
+          <t>Road and bridge infrastructure modernisation programme</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9488,7 +9496,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Technological Change</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -9520,28 +9528,28 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Public sector performance and welfare data systems</t>
+          <t>Social welfare, community and civic facilities development</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9551,7 +9559,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -9583,13 +9591,13 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Road and bridge infrastructure modernisation programme</t>
+          <t>Environmental regulation and impact assessment enforcement</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9599,12 +9607,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9614,7 +9622,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -9646,23 +9654,23 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Social welfare, community and civic facilities development</t>
+          <t>Integrated industrial diversification, FDI and MSME competitiveness strategy</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9677,7 +9685,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -9709,38 +9717,38 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Environmental regulation and impact assessment enforcement</t>
+          <t>Industrial and business site infrastructure provision</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -9772,38 +9780,38 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Integrated industrial diversification, FDI and MSME competitiveness strategy</t>
+          <t>Government facilities and administrative infrastructure upgrading</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -9835,7 +9843,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Government facilities and administrative infrastructure upgrading</t>
+          <t>Unfunded or cross-cutting public-private and institutional capacity measures</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -9846,7 +9854,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9898,23 +9906,23 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unfunded or cross-cutting public-private and institutional capacity measures</t>
+          <t>Non-oil and gas sector competitiveness and export diversification strategy</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9929,7 +9937,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Demographic Shifts; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -9961,18 +9969,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>National Entrepreneurship Agenda</t>
+          <t>Business environment and regulatory reform for private sector development</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9992,7 +10000,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -10024,28 +10032,28 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Non-oil and gas sector competitiveness and export diversification strategy</t>
+          <t>Crime prevention, policing and national security capability strengthening</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10055,7 +10063,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Democratic Backsliding; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -10087,23 +10095,23 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Business environment and regulatory reform for private sector development</t>
+          <t>Community welfare, housing-community religious facilities and social support</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10118,7 +10126,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -10150,18 +10158,18 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Crime prevention, policing and national security capability strengthening</t>
+          <t>Religious education and youth spiritual development</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10171,19 +10179,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Increased Polarisation; Technological Change</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="n">
         <v>0</v>
       </c>
@@ -10213,23 +10213,23 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Community welfare, housing-community religious facilities and social support</t>
+          <t>Diplomatic premises development and international representation support</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10237,16 +10237,8 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="n">
         <v>0</v>
       </c>
@@ -10276,7 +10268,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Diplomatic premises development and international representation support</t>
+          <t>Whole-of-government strategic coordination and implementation reform</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -10287,12 +10279,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10331,13 +10323,13 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Whole-of-government strategic coordination and implementation reform</t>
+          <t>Environmental governance, standards and cooperation</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10355,8 +10347,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K154" t="n">
         <v>0</v>
       </c>
@@ -10386,18 +10386,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Environmental governance, standards and cooperation</t>
+          <t>Human capital funds and private participation in education services</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10412,12 +10412,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -10449,18 +10449,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Human capital funds and private participation in education services</t>
+          <t>Youth civic values and social cohesion development</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -10512,23 +10512,23 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Youth civic values and social cohesion development</t>
+          <t>Public transport and national road infrastructure upgrading programme</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10538,12 +10538,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Public transport and national road infrastructure upgrading programme</t>
+          <t>Port and logistics infrastructure expansion programme</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10599,16 +10599,8 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="n">
         <v>0</v>
       </c>
@@ -10638,23 +10630,23 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Port and logistics infrastructure expansion programme</t>
+          <t>National info-communication and broadcasting infrastructure development programme</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10662,8 +10654,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K159" t="n">
         <v>0</v>
       </c>
@@ -10693,18 +10693,18 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>National info-communication and broadcasting infrastructure development programme</t>
+          <t>Institutional development and civil service modernisation programme</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -10717,16 +10717,8 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="n">
         <v>0</v>
       </c>
@@ -10756,23 +10748,23 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Institutional development and civil service modernisation programme</t>
+          <t>Public buildings and social infrastructure construction programme</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10811,23 +10803,23 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Public buildings and social infrastructure construction programme</t>
+          <t>Unfunded social cohesion and civic participation strategy</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10835,8 +10827,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding</t>
+        </is>
+      </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>122.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13058,12 +13058,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>886652.4</v>
+        <v>13474.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13163,12 +13163,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Environmental Education</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
+          <t>Environmental Education</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
+          <t>Basic Education Democratic, with Quality and Equity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51241.7</v>
+        <v>68424.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Primary Health Care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>135.2</v>
+        <v>51241.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -13373,12 +13373,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13474.9</v>
+        <v>13130.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13130.8</v>
+        <v>12297.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -13618,12 +13618,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13635,7 +13635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13644,7 +13644,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12297.7</v>
+        <v>8397</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -13653,12 +13653,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8397</v>
+        <v>6472.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -13688,12 +13688,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6472.2</v>
+        <v>6801</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6801</v>
+        <v>6183</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>Professional and Technological Education that Transforms</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6183</v>
+        <v>4085.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4085.3</v>
+        <v>557.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -13828,12 +13828,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+          <t>Family Farming and Agroecology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1870.2</v>
+        <v>7781</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>215.9</v>
+        <v>1870.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14379,7 +14379,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7781</v>
+        <v>592.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -14405,7 +14405,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>592.4</v>
+        <v>478</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14449,7 +14449,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>557.9</v>
+        <v>399.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14475,7 +14475,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Road Safety</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>478</v>
+        <v>328.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -14493,12 +14493,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>State Transformation for Citizenship and Development</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>399.2</v>
+        <v>286.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -14545,7 +14545,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>328.8</v>
+        <v>286.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>286.4</v>
+        <v>264.7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14624,7 +14624,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>286.4</v>
+        <v>259.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14633,12 +14633,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>264.7</v>
+        <v>337.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Women Living Free from Violence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>259.5</v>
+        <v>230.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>337.8</v>
+        <v>223.3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -14738,12 +14738,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>230.2</v>
+        <v>222.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+          <t>Sustainable Fisheries and Aquaculture</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>223.3</v>
+        <v>215.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -14808,12 +14808,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>Risk and Disaster Management</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>222.5</v>
+        <v>1905.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -14843,12 +14843,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>108.1</v>
+        <v>213.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1905.3</v>
+        <v>163.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14939,7 +14939,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>213.3</v>
+        <v>4810.6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -14948,12 +14948,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>163.9</v>
+        <v>150.7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Electric Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4810.6</v>
+        <v>143</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -15018,12 +15018,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>150.7</v>
+        <v>139.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
+          <t>Planning and Budgeting for Sustainable Development</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>139.8</v>
+        <v>135.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>136</v>
+        <v>135.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -15158,12 +15158,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+          <t>Economic Autonomy of Women</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15184,7 +15184,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>135.5</v>
+        <v>122.3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>66.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -15333,12 +15333,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
+          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>150</v>
+        <v>472.3</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
+          <t>Electricity supply projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>472.3</v>
+        <v>400</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Electricity supply projects under the 12th National Development Plan</t>
+          <t>National housing provision projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>400</v>
+        <v>277</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>National housing provision projects under the 12th National Development Plan</t>
+          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -16374,7 +16374,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>277</v>
+        <v>261.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
+          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>261.1</v>
+        <v>256.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
+          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>256.5</v>
+        <v>150</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
+          <t>Education information and data management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>29.4</v>
+        <v>21.2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
+          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>27.5</v>
+        <v>19.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Quality health service support provision</t>
+          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26.9</v>
+        <v>29.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -17048,12 +17048,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
+          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -17074,7 +17074,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>25.8</v>
+        <v>27.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Natural disaster management</t>
+          <t>Quality health service support provision</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
+          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>24.1</v>
+        <v>25.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
+          <t>Natural disaster management</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -17179,7 +17179,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -17188,12 +17188,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Education information and data management systems under the 12th National Development Plan</t>
+          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>21.2</v>
+        <v>24.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -17223,12 +17223,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
+          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>19.4</v>
+        <v>24</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2209d3eb-b953-4eef-9a85-64eb1ad9bba8</t>
+          <t>276f0c5d-9953-42f1-970c-4438edd7dbbb</t>
         </is>
       </c>
     </row>
@@ -21985,7 +21985,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>aa53189f-f8bb-4f72-a59a-fc49b059aafb</t>
+          <t>cd36d9e8-1d8d-48d9-8d4d-66dfd8752745</t>
         </is>
       </c>
     </row>
@@ -22033,7 +22033,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2cbc519b-0f4e-4b90-831d-c4c2d7b3b200</t>
+          <t>1601d8a2-b9e7-4f6a-9410-3c950613fa10</t>
         </is>
       </c>
     </row>

--- a/UNION_PANEL.xlsx
+++ b/UNION_PANEL.xlsx
@@ -519,17 +519,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -562,12 +562,12 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>66.90000000000001</v>
+        <v>557.9</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>66.90000000000001</v>
+        <v>557.9</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -588,27 +588,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5123</t>
-        </is>
-      </c>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,7 +619,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -631,12 +627,12 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>13474.9</v>
+        <v>478</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>13474.9</v>
+        <v>478</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -657,10 +653,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -696,12 +696,12 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>886652.4</v>
+        <v>20.1</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>886652.4</v>
+        <v>20.1</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -722,14 +722,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -737,12 +733,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -750,19 +746,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Demographic Shifts</t>
+        </is>
+      </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -783,12 +787,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +802,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -811,27 +815,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -852,22 +848,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -887,7 +883,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -895,12 +891,12 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -921,22 +917,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Labor</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -956,7 +952,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -964,12 +960,12 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -990,22 +986,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Environmental Education</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Labor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1020,25 +1016,25 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1059,10 +1055,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Environmental Education</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Education</t>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1085,25 +1085,25 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Pandemics; Technological Change</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1124,10 +1124,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Health and Environment Surveillance</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Health</t>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1163,12 +1167,12 @@
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>51241.7</v>
+        <v>13474.9</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>51241.7</v>
+        <v>13474.9</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1189,22 +1193,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>5814</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1224,12 +1228,12 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>27428.4</v>
+        <v>18.1</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>27428.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1250,27 +1254,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
+          <t>Basic Education Democratic, with Quality and Equity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1278,19 +1278,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Demographic Shifts; Pandemics; Technological Change</t>
+        </is>
+      </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>22632</v>
+        <v>68424.8</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>22632</v>
+        <v>68424.8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1311,14 +1319,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5121</t>
-        </is>
-      </c>
+          <t>Primary Health Care</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Health</t>
@@ -1331,7 +1335,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1354,12 +1358,12 @@
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>15913.4</v>
+        <v>51241.7</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>15913.4</v>
+        <v>51241.7</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1380,18 +1384,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Better Cities</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5117</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Urban Development</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1404,27 +1412,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>16875</v>
+        <v>27428.4</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>16875</v>
+        <v>27428.4</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1445,51 +1445,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>National Defense</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Shifts in Globalisation</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>13846.4</v>
+        <v>22632</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>13846.4</v>
+        <v>22632</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1510,27 +1506,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1545,7 +1541,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1553,12 +1549,12 @@
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>13130.8</v>
+        <v>15913.4</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>13130.8</v>
+        <v>15913.4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1579,22 +1575,18 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2320</t>
-        </is>
-      </c>
+          <t>Better Cities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Urban Development</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1609,25 +1601,25 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>12297.7</v>
+        <v>16875</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>12297.7</v>
+        <v>16875</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1648,22 +1640,18 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
+          <t>National Defense</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1673,17 +1661,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution</t>
+          <t>Democratic Backsliding; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1691,12 +1679,12 @@
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>8397</v>
+        <v>13846.4</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>8397</v>
+        <v>13846.4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1717,23 +1705,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Road Transport</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1748,20 +1740,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>6472.2</v>
+        <v>13130.8</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>6472.2</v>
+        <v>13130.8</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1782,23 +1774,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Decent Housing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1806,19 +1802,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>6801</v>
+        <v>12297.7</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>6801</v>
+        <v>12297.7</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1839,27 +1843,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1869,12 +1873,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1882,12 +1886,12 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>6183</v>
+        <v>8397</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>6183</v>
+        <v>8397</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1908,18 +1912,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1939,20 +1943,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Increased Polarisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>4085.3</v>
+        <v>6472.2</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>4085.3</v>
+        <v>6472.2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1973,22 +1977,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>3104</t>
-        </is>
-      </c>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2001,27 +2001,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>557.9</v>
+        <v>6801</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>557.9</v>
+        <v>6801</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2042,22 +2034,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2077,7 +2069,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2085,12 +2077,12 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>4015.2</v>
+        <v>6183</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>4015.2</v>
+        <v>6183</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -2111,22 +2103,18 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
-      </c>
+          <t>Professional and Technological Education that Transforms</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2141,12 +2129,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2154,12 +2142,12 @@
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>3396.6</v>
+        <v>4085.3</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>3396.6</v>
+        <v>4085.3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2180,22 +2168,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2208,19 +2196,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+        </is>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>2584.2</v>
+        <v>399.2</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>2584.2</v>
+        <v>399.2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2241,27 +2237,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tourism</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2269,19 +2265,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Environmental Degradation and Pollution; Pandemics; Resource and Energy Pressures; Technological Change</t>
+        </is>
+      </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>2557.2</v>
+        <v>4015.2</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>2557.2</v>
+        <v>4015.2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2302,22 +2306,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2330,19 +2334,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Climate Change</t>
+        </is>
+      </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>6546.1</v>
+        <v>3396.6</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>6546.1</v>
+        <v>3396.6</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2363,18 +2375,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Indigenous Health</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5122</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2387,27 +2403,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>2102.4</v>
+        <v>2584.2</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>2102.4</v>
+        <v>2584.2</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2428,23 +2436,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>Tourism, This Is the Destination</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Tourism</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2459,12 +2471,12 @@
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>2026.6</v>
+        <v>2557.2</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>2026.6</v>
+        <v>2557.2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2485,27 +2497,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2520,12 +2532,12 @@
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>2000</v>
+        <v>6546.1</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>2000</v>
+        <v>6546.1</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2546,18 +2558,18 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
+          <t>Communications for Inclusion and Transformation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2572,12 +2584,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2585,12 +2597,12 @@
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>7781</v>
+        <v>2102.4</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>7781</v>
+        <v>2102.4</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2611,17 +2623,13 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
+          <t>Right to Culture</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2639,27 +2647,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="n">
         <v>1</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>1870.2</v>
+        <v>2026.6</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1870.2</v>
+        <v>2026.6</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2680,27 +2680,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Sport</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2708,27 +2708,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="n">
         <v>1</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>1870.2</v>
+        <v>2000</v>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1870.2</v>
+        <v>2000</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2749,23 +2741,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
+          <t>Family Farming and Agroecology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2775,12 +2767,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2788,12 +2780,12 @@
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>1125</v>
+        <v>7781</v>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1125</v>
+        <v>7781</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2814,23 +2806,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2838,19 +2834,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K37" t="n">
         <v>1</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>1104.2</v>
+        <v>1870.2</v>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1104.2</v>
+        <v>1870.2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2871,23 +2875,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Innovation in Enterprises for a New Industrialization</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2895,19 +2903,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>1054.1</v>
+        <v>1870.2</v>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1054.1</v>
+        <v>1870.2</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2928,23 +2944,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2959,20 +2975,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Democratic Backsliding; Increased Polarisation; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>23058</v>
+        <v>1125</v>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>23058</v>
+        <v>1125</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2993,27 +3009,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>5136</t>
-        </is>
-      </c>
+          <t>Rail Transport</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3028,12 +3040,12 @@
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>592.4</v>
+        <v>1104.2</v>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>592.4</v>
+        <v>1104.2</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -3054,7 +3066,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Cooperation of Defence for National Development</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3065,12 +3077,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3078,27 +3090,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
         <v>1</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>478</v>
+        <v>1054.1</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>478</v>
+        <v>1054.1</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -3119,14 +3123,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
-      </c>
+          <t>Supply and Food Sovereignty</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Agriculture</t>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3149,25 +3149,25 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
-        <v>399.2</v>
+        <v>23058</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>399.2</v>
+        <v>23058</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -3188,27 +3188,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3216,27 +3216,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>1</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>328.8</v>
+        <v>592.4</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>328.8</v>
+        <v>592.4</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3257,23 +3249,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>Road Safety</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3108</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3296,12 +3292,12 @@
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>286.4</v>
+        <v>328.8</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>286.4</v>
+        <v>328.8</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3322,27 +3318,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
+          <t>State Transformation for Citizenship and Development</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3391,23 +3383,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3415,19 +3411,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Technological Change</t>
+        </is>
+      </c>
       <c r="K46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="n">
-        <v>264.7</v>
+        <v>286.4</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>264.7</v>
+        <v>286.4</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3448,14 +3452,10 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2315</t>
-        </is>
-      </c>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3476,27 +3476,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="n">
-        <v>259.5</v>
+        <v>264.7</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>259.5</v>
+        <v>264.7</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3517,10 +3509,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -3543,12 +3539,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3556,12 +3552,12 @@
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="n">
-        <v>337.8</v>
+        <v>259.5</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>337.8</v>
+        <v>259.5</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3582,18 +3578,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3613,7 +3609,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3621,12 +3617,12 @@
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
-        <v>230.2</v>
+        <v>337.8</v>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>230.2</v>
+        <v>337.8</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3647,27 +3643,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>5134</t>
-        </is>
-      </c>
+          <t>Women Living Free from Violence</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3675,19 +3667,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>223.3</v>
+        <v>230.2</v>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>223.3</v>
+        <v>230.2</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3708,23 +3708,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3735,16 +3739,16 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="n">
-        <v>222.5</v>
+        <v>223.3</v>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>222.5</v>
+        <v>223.3</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3765,23 +3769,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3789,27 +3793,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="n">
-        <v>215.9</v>
+        <v>222.5</v>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>215.9</v>
+        <v>222.5</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3830,18 +3826,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
+          <t>Sustainable Fisheries and Aquaculture</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3856,12 +3852,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -3869,12 +3865,12 @@
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="n">
-        <v>1905.3</v>
+        <v>215.9</v>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>1905.3</v>
+        <v>215.9</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3895,22 +3891,18 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
-      </c>
+          <t>Risk and Disaster Management</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3925,12 +3917,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Pandemics</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3938,12 +3930,12 @@
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="n">
-        <v>213.3</v>
+        <v>1905.3</v>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>213.3</v>
+        <v>1905.3</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3964,27 +3956,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3999,7 +3991,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Environmental Degradation and Pollution; Pandemics</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -4007,12 +3999,12 @@
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="n">
-        <v>163.9</v>
+        <v>213.3</v>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>163.9</v>
+        <v>213.3</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -4033,22 +4025,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5133</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4063,12 +4055,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Climate Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -4076,12 +4068,12 @@
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
-        <v>4810.6</v>
+        <v>163.9</v>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>4810.6</v>
+        <v>163.9</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -4102,22 +4094,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Science and Technology</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4132,12 +4124,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -4145,12 +4137,12 @@
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="n">
-        <v>150.7</v>
+        <v>4810.6</v>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>150.7</v>
+        <v>4810.6</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -4171,23 +4163,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Brazilian Space Programme</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Science and Technology</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4197,12 +4193,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Climate Change; Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -4210,12 +4206,12 @@
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="n">
-        <v>143</v>
+        <v>150.7</v>
       </c>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>143</v>
+        <v>150.7</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -4236,27 +4232,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
+          <t>Electric Energy</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4266,12 +4258,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Climate Change; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -4279,12 +4271,12 @@
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
-        <v>139.8</v>
+        <v>143</v>
       </c>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="n">
-        <v>139.8</v>
+        <v>143</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -4305,27 +4297,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4340,7 +4332,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -4348,12 +4340,12 @@
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="n">
-        <v>136</v>
+        <v>139.8</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="n">
-        <v>136</v>
+        <v>139.8</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4374,12 +4366,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+          <t>Planning and Budgeting for Sustainable Development</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4389,12 +4381,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4404,12 +4396,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4417,12 +4409,12 @@
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4443,12 +4435,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4458,7 +4450,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4473,12 +4465,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation</t>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4486,12 +4478,12 @@
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>135.2</v>
+        <v>135.5</v>
       </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
-        <v>135.2</v>
+        <v>135.5</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4512,18 +4504,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Transparency, Integrity and Anti-Corruption</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4543,7 +4539,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Democratic Backsliding; Increased Polarisation</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4551,12 +4547,12 @@
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="n">
-        <v>122.3</v>
+        <v>135.2</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="n">
-        <v>122.3</v>
+        <v>135.2</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4577,7 +4573,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Economic Autonomy of Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -4588,12 +4584,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4601,19 +4597,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K64" t="n">
         <v>1</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="n">
-        <v>108.1</v>
+        <v>122.3</v>
       </c>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
-        <v>108.1</v>
+        <v>122.3</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4634,14 +4638,10 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>5816</t>
-        </is>
-      </c>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -4649,40 +4649,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
         <v>1</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4703,12 +4695,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4728,22 +4720,30 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Demographic Shifts; Increased Polarisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K66" t="n">
         <v>1</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4764,12 +4764,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4792,27 +4792,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="n">
         <v>1</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4833,22 +4825,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Social protection</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4868,7 +4860,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Technological Change</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -4876,12 +4868,12 @@
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="n">
-        <v>467.3</v>
+        <v>76</v>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
-        <v>467.3</v>
+        <v>76</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4902,23 +4894,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4928,12 +4924,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -4941,12 +4937,12 @@
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="n">
-        <v>74.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="n">
-        <v>74.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4967,22 +4963,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
+          <t>Nuclear Policy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4995,19 +4991,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures; Technological Change</t>
+        </is>
+      </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
-        <v>48.8</v>
+        <v>467.3</v>
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
-        <v>48.8</v>
+        <v>467.3</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -5039,12 +5043,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5054,12 +5058,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Democratic Backsliding</t>
+          <t>Climate Change; Democratic Backsliding; Environmental Degradation and Pollution; Increased Polarisation; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -5067,12 +5071,12 @@
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
-        <v>45</v>
+        <v>74.3</v>
       </c>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
-        <v>45</v>
+        <v>74.3</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -5093,10 +5097,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Youth: Rights, Participation and Good Living</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>5135</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -5117,27 +5125,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="n">
         <v>1</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="n">
-        <v>42.1</v>
+        <v>48.8</v>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
-        <v>42.1</v>
+        <v>48.8</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -5158,27 +5158,23 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
+          <t>Institutional Security</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,12 +5184,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+          <t>Democratic Backsliding</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -5201,12 +5197,12 @@
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="n">
-        <v>30.8</v>
+        <v>45</v>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>30.8</v>
+        <v>45</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -5227,7 +5223,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -5238,12 +5234,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5251,19 +5247,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Increased Polarisation</t>
+        </is>
+      </c>
       <c r="K74" t="n">
         <v>1</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="n">
-        <v>28</v>
+        <v>42.1</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="n">
-        <v>28</v>
+        <v>42.1</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -5284,22 +5288,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+          <t>Environmental Quality in Cities and the Countryside</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Social protection</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5312,19 +5316,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution</t>
+        </is>
+      </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="n">
-        <v>27.2</v>
+        <v>30.8</v>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="n">
-        <v>27.2</v>
+        <v>30.8</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -5345,7 +5357,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5356,12 +5368,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5369,27 +5381,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Increased Polarisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="n">
         <v>1</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5410,12 +5414,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5430,7 +5434,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5438,27 +5442,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Demographic Shifts</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="n">
         <v>1</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="n">
-        <v>20.1</v>
+        <v>27.2</v>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="n">
-        <v>20.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -5479,14 +5475,10 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>5814</t>
-        </is>
-      </c>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Social protection</t>
@@ -5494,7 +5486,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5507,19 +5499,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Increased Polarisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="n">
-        <v>18.1</v>
+        <v>34.8</v>
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="n">
-        <v>18.1</v>
+        <v>34.8</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -6596,28 +6596,28 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>National Education System Strengthening</t>
+          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6627,20 +6627,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Climate Change; Democratic Backsliding; Demographic Shifts; Increased Polarisation; Pandemics</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
-        <v>599.2</v>
+        <v>37</v>
       </c>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
-        <v>599.2</v>
+        <v>37</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
+          <t>National Education System Strengthening</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6692,20 +6692,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Shifts in Globalisation; Technological Change</t>
+          <t>Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
-        <v>472.3</v>
+        <v>599.2</v>
       </c>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="n">
-        <v>472.3</v>
+        <v>599.2</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -6726,18 +6726,18 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Electricity supply projects under the 12th National Development Plan</t>
+          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Biodiversity Loss; Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -6766,11 +6766,11 @@
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
-        <v>400</v>
+        <v>472.3</v>
       </c>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="n">
-        <v>400</v>
+        <v>472.3</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
@@ -6791,18 +6791,18 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>National housing provision projects under the 12th National Development Plan</t>
+          <t>Electricity supply projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Housing</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -6831,11 +6831,11 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="n">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -6856,13 +6856,13 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
+          <t>National housing provision projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Housing</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -6896,11 +6896,11 @@
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
-        <v>261.1</v>
+        <v>277</v>
       </c>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
-        <v>261.1</v>
+        <v>277</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -6921,18 +6921,18 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
+          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6942,17 +6942,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -6961,11 +6961,11 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
-        <v>256.5</v>
+        <v>261.1</v>
       </c>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="n">
-        <v>256.5</v>
+        <v>261.1</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
+          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7002,27 +7002,35 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Pandemics</t>
+        </is>
+      </c>
       <c r="K101" t="n">
         <v>1</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
-        <v>150</v>
+        <v>256.5</v>
       </c>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="n">
-        <v>150</v>
+        <v>256.5</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -7043,23 +7051,23 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
+          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Digital</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7067,27 +7075,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Technological Change</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
-        <v>144.7</v>
+        <v>150</v>
       </c>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="n">
-        <v>144.7</v>
+        <v>150</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7108,18 +7108,18 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
+          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Digital</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7139,20 +7139,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Pandemics</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
-        <v>126.6</v>
+        <v>144.7</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>126.6</v>
+        <v>144.7</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
@@ -7173,23 +7173,23 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
+          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7197,19 +7197,27 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Biodiversity Loss; Climate Change; Environmental Degradation and Pollution; Pandemics</t>
+        </is>
+      </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
-        <v>89</v>
+        <v>126.6</v>
       </c>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
-        <v>89</v>
+        <v>126.6</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
@@ -7230,23 +7238,23 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
+          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7254,27 +7262,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Resource and Energy Pressures; Shifts in Globalisation</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
+          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
+          <t>Resource and Energy Pressures; Shifts in Globalisation</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -7335,11 +7335,11 @@
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="n">
-        <v>68.3</v>
+        <v>80</v>
       </c>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
-        <v>68.3</v>
+        <v>80</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
@@ -7360,18 +7360,18 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Flood prevention projects under the 12th National Development Plan</t>
+          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7400,11 +7400,11 @@
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
-        <v>62.5</v>
+        <v>68.3</v>
       </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
-        <v>62.5</v>
+        <v>68.3</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
@@ -7425,23 +7425,23 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bru-HIMS 2.0 system project</t>
+          <t>Flood prevention projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K108" t="n">
@@ -7490,13 +7490,13 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Research and innovation allocations under the 12th National Development Plan</t>
+          <t>Bru-HIMS 2.0 system project</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -7530,11 +7530,11 @@
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
@@ -7555,18 +7555,18 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
+          <t>Research and innovation allocations under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Resource and Energy Pressures; Technological Change</t>
+          <t>Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K110" t="n">
@@ -7595,11 +7595,11 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
@@ -7620,23 +7620,23 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Green Building initiatives under the 12th National Development Plan</t>
+          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
+          <t>Climate Change; Democratic Backsliding; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -7660,11 +7660,11 @@
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -7685,23 +7685,23 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
+          <t>Green Building initiatives under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Technological Change</t>
+          <t>Climate Change; Environmental Degradation and Pollution; Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -7725,11 +7725,11 @@
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
-        <v>37.3</v>
+        <v>50</v>
       </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
-        <v>37.3</v>
+        <v>50</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -7750,18 +7750,18 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
+          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Climate Change; Democratic Backsliding; Demographic Shifts; Increased Polarisation; Pandemics</t>
+          <t>Demographic Shifts; Technological Change</t>
         </is>
       </c>
       <c r="K113" t="n">
@@ -7790,11 +7790,11 @@
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -7945,13 +7945,13 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Education information and data management systems under the 12th National Development Plan</t>
+          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Resource and Energy Pressures; Technological Change</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -7985,11 +7985,11 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
-        <v>21.2</v>
+        <v>29.4</v>
       </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
-        <v>21.2</v>
+        <v>29.4</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
+          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8031,22 +8031,30 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Democratic Backsliding; Shifts in Globalisation; Technological Change</t>
+        </is>
+      </c>
       <c r="K117" t="n">
         <v>1</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
-        <v>19.4</v>
+        <v>27.5</v>
       </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="n">
-        <v>19.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -8067,23 +8075,23 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
+          <t>Quality health service support provision</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8093,12 +8101,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures; Technological Change</t>
+          <t>Pandemics</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -8107,11 +8115,11 @@
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
@@ -8132,38 +8140,38 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
+          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Shifts in Globalisation; Technological Change</t>
+          <t>Resource and Energy Pressures</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -8172,11 +8180,11 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -8197,18 +8205,18 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Quality health service support provision</t>
+          <t>Natural disaster management</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8218,17 +8226,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Pandemics</t>
+          <t>Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Pandemics; Technological Change</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -8237,11 +8245,11 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -8262,13 +8270,13 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
+          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8278,7 +8286,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8293,7 +8301,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -8302,11 +8310,11 @@
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
-        <v>25.8</v>
+        <v>24.1</v>
       </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
-        <v>25.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
@@ -8327,38 +8335,38 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Natural disaster management</t>
+          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Climate Change; Demographic Shifts; Environmental Degradation and Pollution; Pandemics; Technological Change</t>
+          <t>Demographic Shifts; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -8367,11 +8375,11 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -8392,7 +8400,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
+          <t>Education information and data management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -8403,12 +8411,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8432,11 +8440,11 @@
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -8457,18 +8465,18 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
+          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8481,27 +8489,19 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Demographic Shifts; Shifts in Globalisation; Technological Change</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="n">
         <v>1</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
-        <v>24</v>
+        <v>19.4</v>
       </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
-        <v>24</v>
+        <v>19.4</v>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
@@ -9213,23 +9213,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Construction programme for sewerage and waste drainage infrastructure systems</t>
+          <t>Port and logistics infrastructure expansion programme</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9237,16 +9237,8 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="n">
         <v>0</v>
       </c>
@@ -9276,23 +9268,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>National security, defence and public safety infrastructure</t>
+          <t>Construction programme for sewerage and waste drainage infrastructure systems</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9302,12 +9294,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Technological Change</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -9339,23 +9331,23 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Public sector performance and welfare data systems</t>
+          <t>National security, defence and public safety infrastructure</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9370,7 +9362,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Democratic Backsliding; Technological Change</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -9402,18 +9394,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>National Entrepreneurship Agenda</t>
+          <t>Public sector performance and welfare data systems</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9906,18 +9898,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Non-oil and gas sector competitiveness and export diversification strategy</t>
+          <t>National Entrepreneurship Agenda</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9937,7 +9929,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Demographic Shifts; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -9969,13 +9961,13 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Business environment and regulatory reform for private sector development</t>
+          <t>Non-oil and gas sector competitiveness and export diversification strategy</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Industry</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -10000,7 +9992,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Shifts in Globalisation; Technological Change</t>
+          <t>Demographic Shifts; Resource and Energy Pressures; Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -10032,38 +10024,38 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Crime prevention, policing and national security capability strengthening</t>
+          <t>Business environment and regulatory reform for private sector development</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
           <t>high</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Democratic Backsliding; Increased Polarisation; Technological Change</t>
+          <t>Shifts in Globalisation; Technological Change</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -10095,13 +10087,13 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Community welfare, housing-community religious facilities and social support</t>
+          <t>Crime prevention, policing and national security capability strengthening</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -10111,12 +10103,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10126,7 +10118,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Democratic Backsliding; Increased Polarisation; Technological Change</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -10158,23 +10150,23 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Religious education and youth spiritual development</t>
+          <t>Community welfare, housing-community religious facilities and social support</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>reactive</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10182,8 +10174,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
@@ -10213,18 +10213,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Diplomatic premises development and international representation support</t>
+          <t>Religious education and youth spiritual development</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Whole-of-government strategic coordination and implementation reform</t>
+          <t>Diplomatic premises development and international representation support</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10323,13 +10323,13 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Environmental governance, standards and cooperation</t>
+          <t>Whole-of-government strategic coordination and implementation reform</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10347,16 +10347,8 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>Environmental Degradation and Pollution</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="n">
         <v>0</v>
       </c>
@@ -10386,18 +10378,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Human capital funds and private participation in education services</t>
+          <t>Environmental governance, standards and cooperation</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10412,12 +10404,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Technological Change</t>
+          <t>Environmental Degradation and Pollution</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -10449,18 +10441,18 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Youth civic values and social cohesion development</t>
+          <t>Human capital funds and private participation in education services</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Social Protection</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10475,12 +10467,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Increased Polarisation</t>
+          <t>Technological Change</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -10512,23 +10504,23 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Public transport and national road infrastructure upgrading programme</t>
+          <t>Youth civic values and social cohesion development</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Social Protection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10538,12 +10530,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Resource and Energy Pressures</t>
+          <t>Increased Polarisation</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -10575,7 +10567,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Port and logistics infrastructure expansion programme</t>
+          <t>Public transport and national road infrastructure upgrading programme</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -10586,7 +10578,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10599,8 +10591,16 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Resource and Energy Pressures</t>
+        </is>
+      </c>
       <c r="K158" t="n">
         <v>0</v>
       </c>
@@ -13040,7 +13040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oil, Gas, Derivatives and Biofuels</t>
+          <t>Civil Aviation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>66.90000000000001</v>
+        <v>557.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Health and Environment Surveillance</t>
+          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13474.9</v>
+        <v>478</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -13093,12 +13093,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Social security: promotion, guarantee of rights and citizenship</t>
+          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>886652.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bolsa Família: Social Protection through Income Transfer</t>
+          <t>Social security: promotion, guarantee of rights and citizenship</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -13154,7 +13154,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>169512</v>
+        <v>886652.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -13163,12 +13163,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
+          <t>Bolsa Família: Social Protection through Income Transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103391.9</v>
+        <v>169512</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -13198,12 +13198,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Specialized Health Care</t>
+          <t>Social Protection through the Unified Social Assistance System (SUAS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -13224,7 +13224,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>93847.39999999999</v>
+        <v>103391.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Promotion of Decent Work, Employment and Income</t>
+          <t>Specialized Health Care</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -13259,7 +13259,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78582.2</v>
+        <v>93847.39999999999</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Environmental Education</t>
+          <t>Promotion of Decent Work, Employment and Income</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>82888.7</v>
+        <v>78582.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Basic Education Democratic, with Quality and Equity</t>
+          <t>Environmental Education</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -13329,7 +13329,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68424.8</v>
+        <v>82888.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primary Health Care</t>
+          <t>Health and Environment Surveillance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -13364,7 +13364,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>51241.7</v>
+        <v>13474.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
+          <t>National Program for Promotion of the Rights of the Homeless Population</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27428.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
+          <t>Basic Education Democratic, with Quality and Equity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22632</v>
+        <v>68424.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -13443,12 +13443,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Management, Work, Education and Digital Transformation in Health</t>
+          <t>Primary Health Care</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15913.4</v>
+        <v>51241.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Better Cities</t>
+          <t>Qualification of Pharmaceutical Assistance in the Unified Health System</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13504,7 +13504,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16875</v>
+        <v>27428.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>National Defense</t>
+          <t>Logistics Efficiency Enhancement through Multimodal Transport</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -13539,7 +13539,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13846.4</v>
+        <v>22632</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -13548,12 +13548,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Road Transport</t>
+          <t>Management, Work, Education and Digital Transformation in Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -13574,7 +13574,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13130.8</v>
+        <v>15913.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -13583,12 +13583,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Decent Housing</t>
+          <t>Better Cities</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -13609,7 +13609,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12297.7</v>
+        <v>16875</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ports and Waterway Transport</t>
+          <t>National Defense</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -13644,7 +13644,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8397</v>
+        <v>13846.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Science, technology and innovation for social development</t>
+          <t>Road Transport</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6472.2</v>
+        <v>13130.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -13688,12 +13688,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
+          <t>Decent Housing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -13714,7 +13714,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6801</v>
+        <v>12297.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Consolidation of the National Science, Technology and Innovation System</t>
+          <t>Ports and Waterway Transport</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6183</v>
+        <v>8397</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Professional and Technological Education that Transforms</t>
+          <t>Science, technology and innovation for social development</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -13784,7 +13784,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4085.3</v>
+        <v>6472.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Civil Aviation</t>
+          <t>Science, Technology and Innovation for Defence and Sovereignty</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>557.9</v>
+        <v>6801</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -13845,7 +13845,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
+          <t>Consolidation of the National Science, Technology and Innovation System</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -13854,7 +13854,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4015.2</v>
+        <v>6183</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Urban Mobility</t>
+          <t>Professional and Technological Education that Transforms</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -13889,7 +13889,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3396.6</v>
+        <v>4085.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -13915,7 +13915,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Indigenous Health</t>
+          <t>Agricultural Research and Innovation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2584.2</v>
+        <v>399.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tourism, This Is the Destination</t>
+          <t>Research, Development, Innovation, Production and Evaluation of Health Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -13959,7 +13959,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2557.2</v>
+        <v>4015.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -13968,12 +13968,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Regional Development and Territorial Planning</t>
+          <t>Urban Mobility</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -13994,7 +13994,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6546.1</v>
+        <v>3396.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Communications for Inclusion and Transformation</t>
+          <t>Indigenous Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14029,7 +14029,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2102.4</v>
+        <v>2584.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Right to Culture</t>
+          <t>Tourism, This Is the Destination</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14064,7 +14064,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2026.6</v>
+        <v>2557.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -14073,12 +14073,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sport for Life</t>
+          <t>Regional Development and Territorial Planning</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2000</v>
+        <v>6546.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -14108,12 +14108,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14125,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Family Farming and Agroecology</t>
+          <t>Communications for Inclusion and Transformation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14134,7 +14134,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7781</v>
+        <v>2102.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -14160,7 +14160,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Neo-industrialization, Business Environment and Economic Participation</t>
+          <t>Right to Culture</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14169,7 +14169,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1870.2</v>
+        <v>2026.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Innovation in Enterprises for a New Industrialization</t>
+          <t>Sport for Life</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14204,7 +14204,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1870.2</v>
+        <v>2000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -14213,12 +14213,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>International Relations and Assistance to Brazilians Abroad</t>
+          <t>Family Farming and Agroecology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14239,7 +14239,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1125</v>
+        <v>7781</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -14248,12 +14248,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Collaborative Leadership</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14265,7 +14265,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rail Transport</t>
+          <t>Neo-industrialization, Business Environment and Economic Participation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1104.2</v>
+        <v>1870.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -14283,12 +14283,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cooperation of Defence for National Development</t>
+          <t>Innovation in Enterprises for a New Industrialization</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1054.1</v>
+        <v>1870.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply and Food Sovereignty</t>
+          <t>International Relations and Assistance to Brazilians Abroad</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14344,7 +14344,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>23058</v>
+        <v>1125</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Collaborative Leadership</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Land Governance, Agrarian Reform and Land Regularization</t>
+          <t>Rail Transport</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14379,7 +14379,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>592.4</v>
+        <v>1104.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Defense of Democracy and Legal Security for Public Policy Innovation</t>
+          <t>Cooperation of Defence for National Development</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>478</v>
+        <v>1054.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -14423,12 +14423,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Agricultural Research and Innovation</t>
+          <t>Supply and Food Sovereignty</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14449,7 +14449,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>399.2</v>
+        <v>23058</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Road Safety</t>
+          <t>Land Governance, Agrarian Reform and Land Regularization</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14484,7 +14484,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>328.8</v>
+        <v>592.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -14493,12 +14493,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development</t>
+          <t>Road Safety</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14519,7 +14519,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>286.4</v>
+        <v>328.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -14528,12 +14528,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14545,7 +14545,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>State Transformation for Citizenship and Development - Digital Government</t>
+          <t>State Transformation for Citizenship and Development</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
+          <t>State Transformation for Citizenship and Development - Digital Government</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>264.7</v>
+        <v>286.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14598,12 +14598,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Economic Policy for Growth and Socioeconomic Development</t>
+          <t>Policies for Quilombolas, Traditional Communities and Peoples, and Indigenous Rights</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14624,7 +14624,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>259.5</v>
+        <v>264.7</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Promotion of Access to Justice and Defense of Rights</t>
+          <t>Economic Policy for Growth and Socioeconomic Development</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>337.8</v>
+        <v>259.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Women Living Free from Violence</t>
+          <t>Promotion of Access to Justice and Defense of Rights</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -14694,7 +14694,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>230.2</v>
+        <v>337.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
+          <t>Women Living Free from Violence</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>223.3</v>
+        <v>230.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -14738,12 +14738,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>reactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14755,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rights and Participation of Indigenous Peoples</t>
+          <t>Care and Reception of Users and Dependents of Alcohol and Drugs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -14764,7 +14764,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>222.5</v>
+        <v>223.3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -14773,12 +14773,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>reactive</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sustainable Fisheries and Aquaculture</t>
+          <t>Rights and Participation of Indigenous Peoples</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -14799,7 +14799,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>215.9</v>
+        <v>222.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -14808,12 +14808,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -14825,7 +14825,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Risk and Disaster Management</t>
+          <t>Sustainable Fisheries and Aquaculture</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -14834,7 +14834,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1905.3</v>
+        <v>215.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Agricultural Defense</t>
+          <t>Risk and Disaster Management</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -14869,7 +14869,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>213.3</v>
+        <v>1905.3</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -14895,7 +14895,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Financial System of the Future</t>
+          <t>Agricultural Defense</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>163.9</v>
+        <v>213.3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -14913,12 +14913,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Food and Nutrition Security and Fight Against Hunger</t>
+          <t>Financial System of the Future</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -14939,7 +14939,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4810.6</v>
+        <v>163.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -14965,7 +14965,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brazilian Space Programme</t>
+          <t>Food and Nutrition Security and Fight Against Hunger</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>150.7</v>
+        <v>4810.6</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Electric Energy</t>
+          <t>Brazilian Space Programme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15009,7 +15009,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>143</v>
+        <v>150.7</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -15018,12 +15018,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15035,7 +15035,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Safe and Sustainable Mining</t>
+          <t>Electric Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15044,7 +15044,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>139.8</v>
+        <v>143</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -15053,12 +15053,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Export-led</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Planning and Budgeting for Sustainable Development</t>
+          <t>Safe and Sustainable Mining</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15079,7 +15079,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>136</v>
+        <v>139.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -15088,12 +15088,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Export-led</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
+          <t>Planning and Budgeting for Sustainable Development</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15114,7 +15114,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>135.5</v>
+        <v>136</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -15123,12 +15123,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Transparency, Integrity and Anti-Corruption</t>
+          <t>Demarcation and Management of Indigenous Territories for Well-Being</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>135.2</v>
+        <v>135.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Economic Autonomy of Women</t>
+          <t>Transparency, Integrity and Anti-Corruption</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15184,7 +15184,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>122.3</v>
+        <v>135.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
+          <t>Economic Autonomy of Women</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>108.1</v>
+        <v>122.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -15228,12 +15228,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15245,7 +15245,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
+          <t>Inclusion of Families in Vulnerable Situations in CadÚnico</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15254,7 +15254,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>90.40000000000001</v>
+        <v>108.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -15263,12 +15263,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
+          <t>Promotion and Integral Protection of the Human Rights of Children and Adolescents</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15289,7 +15289,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>87</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
+          <t>Pluriethnic Cultural and Social Rights for Full Exercise</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15324,7 +15324,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nuclear Policy</t>
+          <t>Promotion of Ethnic-Racial Equality, Combating and Overcoming Racism</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>467.3</v>
+        <v>76</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fostering the Spirit of Change</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
+          <t>Oil, Gas, Derivatives and Biofuels</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -15394,7 +15394,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>74.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -15403,12 +15403,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Civic Engagement</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15420,7 +15420,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Youth: Rights, Participation and Good Living</t>
+          <t>Nuclear Policy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -15429,7 +15429,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>48.8</v>
+        <v>467.3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Fostering the Spirit of Change</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Institutional Security</t>
+          <t>Reconstruction, Expansion and Deepening of Social Participation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>45</v>
+        <v>74.3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -15473,12 +15473,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Civic Engagement</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
+          <t>Youth: Rights, Participation and Good Living</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>42.1</v>
+        <v>48.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Environmental Quality in Cities and the Countryside</t>
+          <t>Institutional Security</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30.8</v>
+        <v>45</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -15543,12 +15543,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Socioeconomic inclusion of the CadÚnico population</t>
+          <t>Policies for Quilombolas, Traditional Peoples and Communities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -15569,7 +15569,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28</v>
+        <v>42.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -15578,12 +15578,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Tackling Structural Exclusion</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
+          <t>Environmental Quality in Cities and the Countryside</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -15604,7 +15604,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>27.2</v>
+        <v>30.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Promotion of the Rights of Persons with Disabilities</t>
+          <t>Socioeconomic inclusion of the CadÚnico population</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15639,7 +15639,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>34.8</v>
+        <v>28</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -15648,12 +15648,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Promotion of the Right to Age and the Human Rights of Older Persons</t>
+          <t>Promotion and Defense of the Rights of LGBTQIA+ Persons</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15674,7 +15674,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>20.1</v>
+        <v>27.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>National Program for Promotion of the Rights of the Homeless Population</t>
+          <t>Promotion of the Rights of Persons with Disabilities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -15709,7 +15709,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>18.1</v>
+        <v>34.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tackling Structural Exclusion</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>National Education System Strengthening</t>
+          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -16234,7 +16234,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>599.2</v>
+        <v>37</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -16243,12 +16243,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
+          <t>National Education System Strengthening</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>472.3</v>
+        <v>599.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Electricity supply projects under the 12th National Development Plan</t>
+          <t>Development of school and higher education institution infrastructure under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -16304,7 +16304,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>400</v>
+        <v>472.3</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>National housing provision projects under the 12th National Development Plan</t>
+          <t>Electricity supply projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -16339,7 +16339,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Growth through Inclusion</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -16365,7 +16365,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
+          <t>National housing provision projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -16374,7 +16374,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>261.1</v>
+        <v>277</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
+          <t>Water supply and sewerage system upgrading projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -16409,7 +16409,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>256.5</v>
+        <v>261.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Growth through Inclusion</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
+          <t>Medical and health infrastructure development under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>150</v>
+        <v>256.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
+          <t>Payment for medical treatment services at Gleneagles Jerudong Park Medical Centre, Brunei Cancer Centre and Brunei Neuroscience, Stroke and Rehabilitation Centre</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -16479,7 +16479,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>144.7</v>
+        <v>150</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -16488,12 +16488,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -16505,7 +16505,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
+          <t>IT Central Procurement projects and software licences for all ministries and government departments</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -16514,7 +16514,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>126.6</v>
+        <v>144.7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
+          <t>Infrastructure and facilities improvement projects to support paddy, livestock and aquaculture production</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -16549,7 +16549,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>89</v>
+        <v>126.6</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -16558,12 +16558,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
+          <t>Purchase of medicines, medical consumables and laboratory testing needs</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -16584,7 +16584,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -16593,12 +16593,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Domestic Integration</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>inactive</t>
         </is>
       </c>
     </row>
@@ -16610,7 +16610,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
+          <t>Infrastructure provision for enhancement of the agricultural industry nationwide - Phase 2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -16619,7 +16619,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>68.3</v>
+        <v>80</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Flood prevention projects under the 12th National Development Plan</t>
+          <t>Capacity enhancement programme for irrigation systems in agricultural development areas nationwide - Phase 2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -16654,7 +16654,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>62.5</v>
+        <v>68.3</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Domestic Integration</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bru-HIMS 2.0 system project</t>
+          <t>Flood prevention projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Research and innovation allocations under the 12th National Development Plan</t>
+          <t>Bru-HIMS 2.0 system project</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -16724,7 +16724,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>61.8</v>
+        <v>62.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16750,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
+          <t>Research and innovation allocations under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -16759,7 +16759,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Green Building initiatives under the 12th National Development Plan</t>
+          <t>Airport infrastructure modernisation projects under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -16794,7 +16794,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -16803,12 +16803,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Efficient Action (Agility)</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
+          <t>Green Building initiatives under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -16829,7 +16829,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>37.3</v>
+        <v>50</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -16838,12 +16838,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Efficient Action (Agility)</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16855,7 +16855,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Management of infectious disease crises and assistance to affected individuals or communities</t>
+          <t>Scholarships through the Ministry of Education and the Ministry of Religious Affairs</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Education information and data management systems under the 12th National Development Plan</t>
+          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -16969,7 +16969,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>21.2</v>
+        <v>29.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
+          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -17004,7 +17004,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>19.4</v>
+        <v>27.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Political Will</t>
+          <t>Joined-up Thinking</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -17030,7 +17030,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Integrated government databases and asset management systems under the 12th National Development Plan</t>
+          <t>Quality health service support provision</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>29.4</v>
+        <v>26.9</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -17048,12 +17048,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Strategic Planning (Anticipation)</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Focus projects to support the budget focus areas for Financial Year 2024/2025</t>
+          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -17074,7 +17074,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Joined-up Thinking</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quality health service support provision</t>
+          <t>Natural disaster management</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -17109,7 +17109,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>26.9</v>
+        <v>25</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -17135,7 +17135,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Maintenance of Bru-HIMS and enhancement of BruHealth system features</t>
+          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -17144,7 +17144,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>25.8</v>
+        <v>24.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Natural disaster management</t>
+          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -17179,7 +17179,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -17188,12 +17188,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>proactive</t>
+          <t>transformative</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17205,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Education digital infrastructure and smart systems under the 12th National Development Plan</t>
+          <t>Education information and data management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -17223,12 +17223,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Strategic Planning (Anticipation)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>transformative</t>
+          <t>proactive</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MPEC programmes: i-Ready, TVET Scheme, Skillsplus, SPIN in Accountancy and Tradeskills</t>
+          <t>Judiciary digital case management systems under the 12th National Development Plan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>24</v>
+        <v>19.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Enhancing Capabilities in Education, Skills, Digital, Health</t>
+          <t>Political Will</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>276f0c5d-9953-42f1-970c-4438edd7dbbb</t>
+          <t>0c65487e-463a-4b8f-8036-58d9d13141e0</t>
         </is>
       </c>
     </row>
@@ -21985,7 +21985,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>cd36d9e8-1d8d-48d9-8d4d-66dfd8752745</t>
+          <t>7af71a3a-008d-4b13-b33a-696b04582450</t>
         </is>
       </c>
     </row>
@@ -22033,7 +22033,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1601d8a2-b9e7-4f6a-9410-3c950613fa10</t>
+          <t>b6962f7d-7ed8-4542-be0f-606ef8c093f5</t>
         </is>
       </c>
     </row>
